--- a/Images_BGA/Results/Reports/PCBA2_03_inspection_report.xlsx
+++ b/Images_BGA/Results/Reports/PCBA2_03_inspection_report.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="28">
   <si>
     <t>image_name</t>
   </si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>PASS</t>
-  </si>
-  <si>
-    <t>FAIL</t>
   </si>
   <si>
     <t>total_balls</t>
@@ -591,31 +588,31 @@
         <v>3</v>
       </c>
       <c r="C4">
-        <v>647</v>
+        <v>633</v>
       </c>
       <c r="D4">
-        <v>831</v>
+        <v>836</v>
       </c>
       <c r="E4">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F4">
-        <v>5541.77</v>
+        <v>5026.55</v>
       </c>
       <c r="G4">
         <v>3</v>
       </c>
       <c r="H4">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I4">
         <v>119</v>
       </c>
       <c r="J4">
-        <v>3.5007</v>
+        <v>3.8794</v>
       </c>
       <c r="K4">
-        <v>2.1473</v>
+        <v>2.3674</v>
       </c>
       <c r="L4" t="s">
         <v>15</v>
@@ -811,31 +808,31 @@
         <v>8</v>
       </c>
       <c r="C9">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="D9">
-        <v>835</v>
+        <v>824</v>
       </c>
       <c r="E9">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F9">
-        <v>6647.61</v>
+        <v>5281.02</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>0.4545</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>0.4545</v>
       </c>
       <c r="L9" t="s">
         <v>15</v>
@@ -855,31 +852,31 @@
         <v>9</v>
       </c>
       <c r="C10">
-        <v>1160</v>
+        <v>1151</v>
       </c>
       <c r="D10">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="E10">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F10">
-        <v>5808.8</v>
+        <v>5026.55</v>
       </c>
       <c r="G10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="L10" t="s">
         <v>15</v>
@@ -899,31 +896,31 @@
         <v>10</v>
       </c>
       <c r="C11">
-        <v>1030</v>
+        <v>1019</v>
       </c>
       <c r="D11">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="E11">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F11">
-        <v>5541.77</v>
+        <v>5281.02</v>
       </c>
       <c r="G11">
         <v>3</v>
       </c>
       <c r="H11">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I11">
         <v>72</v>
       </c>
       <c r="J11">
-        <v>2.4541</v>
+        <v>2.6131</v>
       </c>
       <c r="K11">
-        <v>1.2992</v>
+        <v>1.3634</v>
       </c>
       <c r="L11" t="s">
         <v>15</v>
@@ -987,16 +984,16 @@
         <v>12</v>
       </c>
       <c r="C13">
-        <v>898</v>
+        <v>888</v>
       </c>
       <c r="D13">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="E13">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F13">
-        <v>5541.77</v>
+        <v>5281.02</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1008,10 +1005,10 @@
         <v>19</v>
       </c>
       <c r="J13">
-        <v>0.3429</v>
+        <v>0.3598</v>
       </c>
       <c r="K13">
-        <v>0.3429</v>
+        <v>0.3598</v>
       </c>
       <c r="L13" t="s">
         <v>15</v>
@@ -1075,10 +1072,10 @@
         <v>14</v>
       </c>
       <c r="C15">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="D15">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="E15">
         <v>92</v>
@@ -1087,19 +1084,19 @@
         <v>6647.61</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>0.7221</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>0.4663</v>
       </c>
       <c r="L15" t="s">
         <v>15</v>
@@ -1119,31 +1116,31 @@
         <v>15</v>
       </c>
       <c r="C16">
-        <v>523</v>
+        <v>501</v>
       </c>
       <c r="D16">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="E16">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F16">
-        <v>6647.61</v>
+        <v>5281.02</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>0.8332000000000001</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>0.4545</v>
       </c>
       <c r="L16" t="s">
         <v>15</v>
@@ -1295,31 +1292,31 @@
         <v>19</v>
       </c>
       <c r="C20">
-        <v>1420</v>
+        <v>1425</v>
       </c>
       <c r="D20">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="E20">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="F20">
-        <v>6647.61</v>
+        <v>4536.46</v>
       </c>
       <c r="G20">
         <v>3</v>
       </c>
       <c r="H20">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="I20">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="J20">
-        <v>4.6784</v>
+        <v>6.8115</v>
       </c>
       <c r="K20">
-        <v>3.836</v>
+        <v>5.7534</v>
       </c>
       <c r="L20" t="s">
         <v>15</v>
@@ -1339,31 +1336,31 @@
         <v>20</v>
       </c>
       <c r="C21">
-        <v>1148</v>
+        <v>1161</v>
       </c>
       <c r="D21">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="E21">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F21">
-        <v>6082.12</v>
+        <v>6647.61</v>
       </c>
       <c r="G21">
         <v>3</v>
       </c>
       <c r="H21">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="I21">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="J21">
-        <v>5.1133</v>
+        <v>4.4527</v>
       </c>
       <c r="K21">
-        <v>2.6635</v>
+        <v>2.4069</v>
       </c>
       <c r="L21" t="s">
         <v>15</v>
@@ -1383,31 +1380,31 @@
         <v>21</v>
       </c>
       <c r="C22">
-        <v>763</v>
+        <v>755</v>
       </c>
       <c r="D22">
-        <v>926</v>
+        <v>935</v>
       </c>
       <c r="E22">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F22">
-        <v>6361.73</v>
+        <v>6647.61</v>
       </c>
       <c r="G22">
         <v>2</v>
       </c>
       <c r="H22">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="I22">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J22">
-        <v>3.5997</v>
+        <v>3.3847</v>
       </c>
       <c r="K22">
-        <v>1.8391</v>
+        <v>1.7149</v>
       </c>
       <c r="L22" t="s">
         <v>15</v>
@@ -1427,31 +1424,31 @@
         <v>22</v>
       </c>
       <c r="C23">
-        <v>1021</v>
+        <v>1030</v>
       </c>
       <c r="D23">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="E23">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F23">
-        <v>5026.55</v>
+        <v>5541.77</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23">
-        <v>240</v>
+        <v>281</v>
       </c>
       <c r="I23">
-        <v>240</v>
+        <v>281</v>
       </c>
       <c r="J23">
-        <v>4.7746</v>
+        <v>5.0706</v>
       </c>
       <c r="K23">
-        <v>4.7746</v>
+        <v>5.0706</v>
       </c>
       <c r="L23" t="s">
         <v>15</v>
@@ -1471,31 +1468,31 @@
         <v>23</v>
       </c>
       <c r="C24">
-        <v>1688</v>
+        <v>1708</v>
       </c>
       <c r="D24">
-        <v>926</v>
+        <v>918</v>
       </c>
       <c r="E24">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F24">
-        <v>5808.8</v>
+        <v>6647.61</v>
       </c>
       <c r="G24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H24">
-        <v>145</v>
+        <v>109</v>
       </c>
       <c r="I24">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="J24">
-        <v>2.4962</v>
+        <v>1.6397</v>
       </c>
       <c r="K24">
-        <v>1.3084</v>
+        <v>1.0079</v>
       </c>
       <c r="L24" t="s">
         <v>15</v>
@@ -1515,31 +1512,31 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="D25">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="E25">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F25">
-        <v>5808.8</v>
+        <v>6647.61</v>
       </c>
       <c r="G25">
         <v>2</v>
       </c>
       <c r="H25">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I25">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J25">
-        <v>1.0157</v>
+        <v>0.8274</v>
       </c>
       <c r="K25">
-        <v>0.6025</v>
+        <v>0.5115</v>
       </c>
       <c r="L25" t="s">
         <v>15</v>
@@ -1562,28 +1559,28 @@
         <v>896</v>
       </c>
       <c r="D26">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="E26">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F26">
-        <v>5541.77</v>
+        <v>5281.02</v>
       </c>
       <c r="G26">
         <v>2</v>
       </c>
       <c r="H26">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="I26">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J26">
-        <v>6.6405</v>
+        <v>7.1198</v>
       </c>
       <c r="K26">
-        <v>5.5939</v>
+        <v>5.908</v>
       </c>
       <c r="L26" t="s">
         <v>15</v>
@@ -1603,31 +1600,31 @@
         <v>26</v>
       </c>
       <c r="C27">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="D27">
-        <v>929</v>
+        <v>946</v>
       </c>
       <c r="E27">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F27">
-        <v>5541.77</v>
+        <v>6082.12</v>
       </c>
       <c r="G27">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27">
-        <v>150</v>
+        <v>271</v>
       </c>
       <c r="I27">
-        <v>94</v>
+        <v>271</v>
       </c>
       <c r="J27">
-        <v>2.7067</v>
+        <v>4.4557</v>
       </c>
       <c r="K27">
-        <v>1.6962</v>
+        <v>4.4557</v>
       </c>
       <c r="L27" t="s">
         <v>15</v>
@@ -1691,31 +1688,31 @@
         <v>28</v>
       </c>
       <c r="C29">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="D29">
         <v>931</v>
       </c>
       <c r="E29">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="F29">
-        <v>5541.77</v>
+        <v>4536.46</v>
       </c>
       <c r="G29">
         <v>3</v>
       </c>
       <c r="H29">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="I29">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="J29">
-        <v>7.1638</v>
+        <v>8.839499999999999</v>
       </c>
       <c r="K29">
-        <v>3.1037</v>
+        <v>3.8797</v>
       </c>
       <c r="L29" t="s">
         <v>15</v>
@@ -1779,31 +1776,31 @@
         <v>30</v>
       </c>
       <c r="C31">
-        <v>1947</v>
+        <v>1960</v>
       </c>
       <c r="D31">
-        <v>937</v>
+        <v>918</v>
       </c>
       <c r="E31">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F31">
-        <v>4300.84</v>
+        <v>5281.02</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>3.238</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>2.1019</v>
       </c>
       <c r="L31" t="s">
         <v>15</v>
@@ -1823,16 +1820,16 @@
         <v>31</v>
       </c>
       <c r="C32">
-        <v>622</v>
+        <v>629</v>
       </c>
       <c r="D32">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="E32">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F32">
-        <v>6647.61</v>
+        <v>4778.36</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -1867,31 +1864,31 @@
         <v>32</v>
       </c>
       <c r="C33">
-        <v>1284</v>
+        <v>1293</v>
       </c>
       <c r="D33">
-        <v>940</v>
+        <v>928</v>
       </c>
       <c r="E33">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="F33">
-        <v>6647.61</v>
+        <v>4536.46</v>
       </c>
       <c r="G33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H33">
-        <v>56</v>
+        <v>167</v>
       </c>
       <c r="I33">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="J33">
-        <v>0.8424</v>
+        <v>3.6813</v>
       </c>
       <c r="K33">
-        <v>0.5716</v>
+        <v>1.8737</v>
       </c>
       <c r="L33" t="s">
         <v>15</v>
@@ -1911,31 +1908,31 @@
         <v>33</v>
       </c>
       <c r="C34">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="D34">
-        <v>1006</v>
+        <v>948</v>
       </c>
       <c r="E34">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F34">
-        <v>4071.5</v>
+        <v>3631.68</v>
       </c>
       <c r="G34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H34">
-        <v>129</v>
+        <v>48</v>
       </c>
       <c r="I34">
-        <v>89</v>
+        <v>26</v>
       </c>
       <c r="J34">
-        <v>3.1684</v>
+        <v>1.3217</v>
       </c>
       <c r="K34">
-        <v>2.1859</v>
+        <v>0.7159</v>
       </c>
       <c r="L34" t="s">
         <v>15</v>
@@ -1955,31 +1952,31 @@
         <v>34</v>
       </c>
       <c r="C35">
-        <v>1705</v>
+        <v>1708</v>
       </c>
       <c r="D35">
-        <v>1012</v>
+        <v>1019</v>
       </c>
       <c r="E35">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F35">
-        <v>6361.73</v>
+        <v>5808.8</v>
       </c>
       <c r="G35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H35">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="I35">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J35">
-        <v>1.6819</v>
+        <v>1.2567</v>
       </c>
       <c r="K35">
-        <v>0.6758999999999999</v>
+        <v>0.8091</v>
       </c>
       <c r="L35" t="s">
         <v>15</v>
@@ -1999,31 +1996,31 @@
         <v>35</v>
       </c>
       <c r="C36">
-        <v>1955</v>
+        <v>1960</v>
       </c>
       <c r="D36">
-        <v>1012</v>
+        <v>1017</v>
       </c>
       <c r="E36">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F36">
-        <v>6647.61</v>
+        <v>5541.77</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H36">
-        <v>297</v>
+        <v>327</v>
       </c>
       <c r="I36">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="J36">
-        <v>4.4678</v>
+        <v>5.9006</v>
       </c>
       <c r="K36">
-        <v>3.3847</v>
+        <v>4.1503</v>
       </c>
       <c r="L36" t="s">
         <v>15</v>
@@ -2043,10 +2040,10 @@
         <v>36</v>
       </c>
       <c r="C37">
-        <v>2215</v>
+        <v>2246</v>
       </c>
       <c r="D37">
-        <v>1013</v>
+        <v>1004</v>
       </c>
       <c r="E37">
         <v>92</v>
@@ -2055,19 +2052,19 @@
         <v>6647.61</v>
       </c>
       <c r="G37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H37">
-        <v>750</v>
+        <v>171</v>
       </c>
       <c r="I37">
-        <v>579</v>
+        <v>132</v>
       </c>
       <c r="J37">
-        <v>11.2823</v>
+        <v>2.5724</v>
       </c>
       <c r="K37">
-        <v>8.709899999999999</v>
+        <v>1.9857</v>
       </c>
       <c r="L37" t="s">
         <v>15</v>
@@ -2131,10 +2128,10 @@
         <v>38</v>
       </c>
       <c r="C39">
-        <v>2080</v>
+        <v>2095</v>
       </c>
       <c r="D39">
-        <v>1014</v>
+        <v>1036</v>
       </c>
       <c r="E39">
         <v>92</v>
@@ -2143,19 +2140,19 @@
         <v>6647.61</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="I39">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="J39">
-        <v>2.5724</v>
+        <v>0</v>
       </c>
       <c r="K39">
-        <v>2.5724</v>
+        <v>0</v>
       </c>
       <c r="L39" t="s">
         <v>15</v>
@@ -2175,31 +2172,31 @@
         <v>39</v>
       </c>
       <c r="C40">
-        <v>1560</v>
+        <v>1559</v>
       </c>
       <c r="D40">
-        <v>1017</v>
+        <v>1000</v>
       </c>
       <c r="E40">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F40">
-        <v>4778.36</v>
+        <v>5541.77</v>
       </c>
       <c r="G40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H40">
-        <v>313</v>
+        <v>207</v>
       </c>
       <c r="I40">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="J40">
-        <v>6.5504</v>
+        <v>3.7353</v>
       </c>
       <c r="K40">
-        <v>4.5413</v>
+        <v>3.4285</v>
       </c>
       <c r="L40" t="s">
         <v>15</v>
@@ -2219,31 +2216,31 @@
         <v>40</v>
       </c>
       <c r="C41">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="D41">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E41">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F41">
-        <v>5808.8</v>
+        <v>5026.55</v>
       </c>
       <c r="G41">
         <v>5</v>
       </c>
       <c r="H41">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="I41">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J41">
-        <v>4.3899</v>
+        <v>5.1924</v>
       </c>
       <c r="K41">
-        <v>1.9109</v>
+        <v>2.2481</v>
       </c>
       <c r="L41" t="s">
         <v>15</v>
@@ -2263,10 +2260,10 @@
         <v>41</v>
       </c>
       <c r="C42">
-        <v>1165</v>
+        <v>1155</v>
       </c>
       <c r="D42">
-        <v>1020</v>
+        <v>1044</v>
       </c>
       <c r="E42">
         <v>92</v>
@@ -2275,19 +2272,19 @@
         <v>6647.61</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H42">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="J42">
-        <v>0.707</v>
+        <v>0</v>
       </c>
       <c r="K42">
-        <v>0.361</v>
+        <v>0</v>
       </c>
       <c r="L42" t="s">
         <v>15</v>
@@ -2307,31 +2304,31 @@
         <v>42</v>
       </c>
       <c r="C43">
-        <v>641</v>
+        <v>627</v>
       </c>
       <c r="D43">
         <v>1022</v>
       </c>
       <c r="E43">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="F43">
-        <v>6647.61</v>
+        <v>4536.46</v>
       </c>
       <c r="G43">
         <v>3</v>
       </c>
       <c r="H43">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="I43">
-        <v>101</v>
+        <v>156</v>
       </c>
       <c r="J43">
-        <v>2.7077</v>
+        <v>5.4668</v>
       </c>
       <c r="K43">
-        <v>1.5193</v>
+        <v>3.4388</v>
       </c>
       <c r="L43" t="s">
         <v>15</v>
@@ -2395,16 +2392,16 @@
         <v>44</v>
       </c>
       <c r="C45">
-        <v>909</v>
+        <v>898</v>
       </c>
       <c r="D45">
         <v>1022</v>
       </c>
       <c r="E45">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F45">
-        <v>6647.61</v>
+        <v>4778.36</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -2439,31 +2436,31 @@
         <v>45</v>
       </c>
       <c r="C46">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="D46">
         <v>1023</v>
       </c>
       <c r="E46">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F46">
-        <v>5026.55</v>
+        <v>4536.46</v>
       </c>
       <c r="G46">
         <v>2</v>
       </c>
       <c r="H46">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="I46">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="J46">
-        <v>6.585</v>
+        <v>7.3405</v>
       </c>
       <c r="K46">
-        <v>3.4417</v>
+        <v>3.7254</v>
       </c>
       <c r="L46" t="s">
         <v>15</v>
@@ -2483,31 +2480,31 @@
         <v>46</v>
       </c>
       <c r="C47">
-        <v>510</v>
+        <v>493</v>
       </c>
       <c r="D47">
         <v>1023</v>
       </c>
       <c r="E47">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="F47">
-        <v>6647.61</v>
+        <v>4536.46</v>
       </c>
       <c r="G47">
         <v>2</v>
       </c>
       <c r="H47">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="I47">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="J47">
-        <v>4.2873</v>
+        <v>6.3486</v>
       </c>
       <c r="K47">
-        <v>3.0236</v>
+        <v>4.4969</v>
       </c>
       <c r="L47" t="s">
         <v>15</v>
@@ -2527,31 +2524,31 @@
         <v>47</v>
       </c>
       <c r="C48">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D48">
-        <v>1025</v>
+        <v>1040</v>
       </c>
       <c r="E48">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F48">
-        <v>5281.02</v>
+        <v>6647.61</v>
       </c>
       <c r="G48">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>174</v>
+        <v>72</v>
       </c>
       <c r="I48">
         <v>72</v>
       </c>
       <c r="J48">
-        <v>3.2948</v>
+        <v>1.0831</v>
       </c>
       <c r="K48">
-        <v>1.3634</v>
+        <v>1.0831</v>
       </c>
       <c r="L48" t="s">
         <v>15</v>
@@ -2571,31 +2568,31 @@
         <v>48</v>
       </c>
       <c r="C49">
-        <v>1010</v>
+        <v>1027</v>
       </c>
       <c r="D49">
-        <v>1031</v>
+        <v>1021</v>
       </c>
       <c r="E49">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="F49">
-        <v>6647.61</v>
+        <v>4536.46</v>
       </c>
       <c r="G49">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H49">
-        <v>247</v>
+        <v>294</v>
       </c>
       <c r="I49">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J49">
-        <v>3.7156</v>
+        <v>6.4808</v>
       </c>
       <c r="K49">
-        <v>3.3847</v>
+        <v>5.048</v>
       </c>
       <c r="L49" t="s">
         <v>15</v>
@@ -2615,31 +2612,31 @@
         <v>49</v>
       </c>
       <c r="C50">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="D50">
-        <v>1098</v>
+        <v>1110</v>
       </c>
       <c r="E50">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F50">
-        <v>6647.61</v>
+        <v>6361.73</v>
       </c>
       <c r="G50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H50">
-        <v>209</v>
+        <v>155</v>
       </c>
       <c r="I50">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J50">
-        <v>3.144</v>
+        <v>2.4364</v>
       </c>
       <c r="K50">
-        <v>1.4441</v>
+        <v>1.5719</v>
       </c>
       <c r="L50" t="s">
         <v>15</v>
@@ -2659,31 +2656,31 @@
         <v>50</v>
       </c>
       <c r="C51">
-        <v>1580</v>
+        <v>1561</v>
       </c>
       <c r="D51">
-        <v>1105</v>
+        <v>1110</v>
       </c>
       <c r="E51">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F51">
-        <v>6647.61</v>
+        <v>5281.02</v>
       </c>
       <c r="G51">
         <v>5</v>
       </c>
       <c r="H51">
-        <v>370</v>
+        <v>218</v>
       </c>
       <c r="I51">
-        <v>198</v>
+        <v>107</v>
       </c>
       <c r="J51">
-        <v>5.5659</v>
+        <v>4.128</v>
       </c>
       <c r="K51">
-        <v>2.9785</v>
+        <v>2.0261</v>
       </c>
       <c r="L51" t="s">
         <v>15</v>
@@ -2703,31 +2700,31 @@
         <v>51</v>
       </c>
       <c r="C52">
-        <v>1295</v>
+        <v>1289</v>
       </c>
       <c r="D52">
-        <v>1107</v>
+        <v>1090</v>
       </c>
       <c r="E52">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F52">
-        <v>6361.73</v>
+        <v>6647.61</v>
       </c>
       <c r="G52">
         <v>3</v>
       </c>
       <c r="H52">
-        <v>201</v>
+        <v>724</v>
       </c>
       <c r="I52">
-        <v>149</v>
+        <v>547</v>
       </c>
       <c r="J52">
-        <v>3.1595</v>
+        <v>10.8911</v>
       </c>
       <c r="K52">
-        <v>2.3421</v>
+        <v>8.2285</v>
       </c>
       <c r="L52" t="s">
         <v>15</v>
@@ -2747,16 +2744,16 @@
         <v>52</v>
       </c>
       <c r="C53">
-        <v>2224</v>
+        <v>2248</v>
       </c>
       <c r="D53">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="E53">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F53">
-        <v>6647.61</v>
+        <v>5808.8</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -2791,31 +2788,31 @@
         <v>53</v>
       </c>
       <c r="C54">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D54">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="E54">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F54">
-        <v>6361.73</v>
+        <v>5541.77</v>
       </c>
       <c r="G54">
         <v>2</v>
       </c>
       <c r="H54">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="I54">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="J54">
-        <v>3.3481</v>
+        <v>3.9699</v>
       </c>
       <c r="K54">
-        <v>3.0023</v>
+        <v>3.5548</v>
       </c>
       <c r="L54" t="s">
         <v>15</v>
@@ -2835,31 +2832,31 @@
         <v>54</v>
       </c>
       <c r="C55">
-        <v>1407</v>
+        <v>1426</v>
       </c>
       <c r="D55">
-        <v>1111</v>
+        <v>1108</v>
       </c>
       <c r="E55">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F55">
-        <v>6647.61</v>
+        <v>5541.77</v>
       </c>
       <c r="G55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H55">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="I55">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="J55">
-        <v>2.2113</v>
+        <v>3.1037</v>
       </c>
       <c r="K55">
-        <v>1.9105</v>
+        <v>2.1834</v>
       </c>
       <c r="L55" t="s">
         <v>15</v>
@@ -2879,31 +2876,31 @@
         <v>55</v>
       </c>
       <c r="C56">
-        <v>884</v>
+        <v>889</v>
       </c>
       <c r="D56">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="E56">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F56">
-        <v>5808.8</v>
+        <v>6361.73</v>
       </c>
       <c r="G56">
         <v>5</v>
       </c>
       <c r="H56">
-        <v>244</v>
+        <v>283</v>
       </c>
       <c r="I56">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J56">
-        <v>4.2005</v>
+        <v>4.4485</v>
       </c>
       <c r="K56">
-        <v>2.1003</v>
+        <v>1.902</v>
       </c>
       <c r="L56" t="s">
         <v>15</v>
@@ -2967,31 +2964,31 @@
         <v>57</v>
       </c>
       <c r="C58">
-        <v>1697</v>
+        <v>1707</v>
       </c>
       <c r="D58">
-        <v>1113</v>
+        <v>1108</v>
       </c>
       <c r="E58">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F58">
-        <v>5281.02</v>
+        <v>6082.12</v>
       </c>
       <c r="G58">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H58">
-        <v>338</v>
+        <v>288</v>
       </c>
       <c r="I58">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="J58">
-        <v>6.4003</v>
+        <v>4.7352</v>
       </c>
       <c r="K58">
-        <v>2.6131</v>
+        <v>1.9566</v>
       </c>
       <c r="L58" t="s">
         <v>15</v>
@@ -3011,31 +3008,31 @@
         <v>58</v>
       </c>
       <c r="C59">
-        <v>1960</v>
+        <v>1971</v>
       </c>
       <c r="D59">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="E59">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F59">
-        <v>6647.61</v>
+        <v>5281.02</v>
       </c>
       <c r="G59">
         <v>3</v>
       </c>
       <c r="H59">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="I59">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="J59">
-        <v>4.6784</v>
+        <v>5.4724</v>
       </c>
       <c r="K59">
-        <v>1.8352</v>
+        <v>2.5563</v>
       </c>
       <c r="L59" t="s">
         <v>15</v>
@@ -3055,31 +3052,31 @@
         <v>59</v>
       </c>
       <c r="C60">
-        <v>633</v>
+        <v>621</v>
       </c>
       <c r="D60">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="E60">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F60">
-        <v>6647.61</v>
+        <v>4778.36</v>
       </c>
       <c r="G60">
         <v>2</v>
       </c>
       <c r="H60">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="I60">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J60">
-        <v>2.5122</v>
+        <v>3.6205</v>
       </c>
       <c r="K60">
-        <v>1.7299</v>
+        <v>2.4276</v>
       </c>
       <c r="L60" t="s">
         <v>15</v>
@@ -3146,28 +3143,28 @@
         <v>488</v>
       </c>
       <c r="D62">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="E62">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F62">
-        <v>5281.02</v>
+        <v>4778.36</v>
       </c>
       <c r="G62">
         <v>1</v>
       </c>
       <c r="H62">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I62">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J62">
-        <v>1.4391</v>
+        <v>1.5696</v>
       </c>
       <c r="K62">
-        <v>1.4391</v>
+        <v>1.5696</v>
       </c>
       <c r="L62" t="s">
         <v>15</v>
@@ -3187,31 +3184,31 @@
         <v>62</v>
       </c>
       <c r="C63">
-        <v>2105</v>
+        <v>2104</v>
       </c>
       <c r="D63">
-        <v>1119</v>
+        <v>1111</v>
       </c>
       <c r="E63">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="F63">
-        <v>6647.61</v>
+        <v>5026.55</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I63">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J63">
-        <v>0</v>
+        <v>0.3183</v>
       </c>
       <c r="K63">
-        <v>0</v>
+        <v>0.3183</v>
       </c>
       <c r="L63" t="s">
         <v>15</v>
@@ -3231,31 +3228,31 @@
         <v>63</v>
       </c>
       <c r="C64">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D64">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="E64">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="F64">
-        <v>6361.73</v>
+        <v>4778.36</v>
       </c>
       <c r="G64">
         <v>3</v>
       </c>
       <c r="H64">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="I64">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J64">
-        <v>2.9395</v>
+        <v>4.0809</v>
       </c>
       <c r="K64">
-        <v>1.8863</v>
+        <v>2.595</v>
       </c>
       <c r="L64" t="s">
         <v>15</v>
@@ -3275,10 +3272,10 @@
         <v>64</v>
       </c>
       <c r="C65">
-        <v>1043</v>
+        <v>1028</v>
       </c>
       <c r="D65">
-        <v>1122</v>
+        <v>1105</v>
       </c>
       <c r="E65">
         <v>92</v>
@@ -3287,19 +3284,19 @@
         <v>6647.61</v>
       </c>
       <c r="G65">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H65">
-        <v>78</v>
+        <v>180</v>
       </c>
       <c r="I65">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="J65">
-        <v>1.1734</v>
+        <v>2.7077</v>
       </c>
       <c r="K65">
-        <v>0.7672</v>
+        <v>1.0831</v>
       </c>
       <c r="L65" t="s">
         <v>15</v>
@@ -3319,31 +3316,31 @@
         <v>65</v>
       </c>
       <c r="C66">
-        <v>1035</v>
+        <v>1025</v>
       </c>
       <c r="D66">
-        <v>1194</v>
+        <v>1129</v>
       </c>
       <c r="E66">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="F66">
-        <v>6647.61</v>
+        <v>3631.68</v>
       </c>
       <c r="G66">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H66">
-        <v>437</v>
+        <v>122</v>
       </c>
       <c r="I66">
-        <v>275</v>
+        <v>59</v>
       </c>
       <c r="J66">
-        <v>6.5738</v>
+        <v>3.3593</v>
       </c>
       <c r="K66">
-        <v>4.1368</v>
+        <v>1.6246</v>
       </c>
       <c r="L66" t="s">
         <v>15</v>
@@ -3363,10 +3360,10 @@
         <v>66</v>
       </c>
       <c r="C67">
-        <v>1826</v>
+        <v>1847</v>
       </c>
       <c r="D67">
-        <v>1199</v>
+        <v>1178</v>
       </c>
       <c r="E67">
         <v>92</v>
@@ -3375,16 +3372,16 @@
         <v>6647.61</v>
       </c>
       <c r="G67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H67">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="I67">
         <v>99</v>
       </c>
       <c r="J67">
-        <v>2.091</v>
+        <v>2.6325</v>
       </c>
       <c r="K67">
         <v>1.4893</v>
@@ -3407,10 +3404,10 @@
         <v>67</v>
       </c>
       <c r="C68">
-        <v>2254</v>
+        <v>2262</v>
       </c>
       <c r="D68">
-        <v>1199</v>
+        <v>1205</v>
       </c>
       <c r="E68">
         <v>92</v>
@@ -3419,19 +3416,19 @@
         <v>6647.61</v>
       </c>
       <c r="G68">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H68">
-        <v>219</v>
+        <v>82</v>
       </c>
       <c r="I68">
-        <v>137</v>
+        <v>82</v>
       </c>
       <c r="J68">
-        <v>3.2944</v>
+        <v>1.2335</v>
       </c>
       <c r="K68">
-        <v>2.0609</v>
+        <v>1.2335</v>
       </c>
       <c r="L68" t="s">
         <v>15</v>
@@ -3451,10 +3448,10 @@
         <v>68</v>
       </c>
       <c r="C69">
-        <v>2101</v>
+        <v>2109</v>
       </c>
       <c r="D69">
-        <v>1201</v>
+        <v>1184</v>
       </c>
       <c r="E69">
         <v>92</v>
@@ -3463,19 +3460,19 @@
         <v>6647.61</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H69">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="I69">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="J69">
-        <v>0.361</v>
+        <v>1.1734</v>
       </c>
       <c r="K69">
-        <v>0.361</v>
+        <v>0.5265</v>
       </c>
       <c r="L69" t="s">
         <v>15</v>
@@ -3495,31 +3492,31 @@
         <v>69</v>
       </c>
       <c r="C70">
-        <v>1975</v>
+        <v>1982</v>
       </c>
       <c r="D70">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="E70">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F70">
-        <v>6361.73</v>
+        <v>6647.61</v>
       </c>
       <c r="G70">
         <v>2</v>
       </c>
       <c r="H70">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="I70">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J70">
-        <v>3.9926</v>
+        <v>3.7608</v>
       </c>
       <c r="K70">
-        <v>3.0966</v>
+        <v>2.9183</v>
       </c>
       <c r="L70" t="s">
         <v>15</v>
@@ -3539,16 +3536,16 @@
         <v>70</v>
       </c>
       <c r="C71">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="D71">
-        <v>1207</v>
+        <v>1214</v>
       </c>
       <c r="E71">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F71">
-        <v>6361.73</v>
+        <v>6082.12</v>
       </c>
       <c r="G71">
         <v>6</v>
@@ -3560,10 +3557,10 @@
         <v>51</v>
       </c>
       <c r="J71">
-        <v>2.908</v>
+        <v>3.0417</v>
       </c>
       <c r="K71">
-        <v>0.8017</v>
+        <v>0.8385</v>
       </c>
       <c r="L71" t="s">
         <v>15</v>
@@ -3583,31 +3580,31 @@
         <v>71</v>
       </c>
       <c r="C72">
-        <v>1706</v>
+        <v>1697</v>
       </c>
       <c r="D72">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="E72">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F72">
-        <v>6361.73</v>
+        <v>5808.8</v>
       </c>
       <c r="G72">
         <v>3</v>
       </c>
       <c r="H72">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="I72">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J72">
-        <v>2.2478</v>
+        <v>2.6339</v>
       </c>
       <c r="K72">
-        <v>1.6191</v>
+        <v>1.8592</v>
       </c>
       <c r="L72" t="s">
         <v>15</v>
@@ -3627,31 +3624,31 @@
         <v>72</v>
       </c>
       <c r="C73">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D73">
-        <v>1210</v>
+        <v>1196</v>
       </c>
       <c r="E73">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F73">
-        <v>5541.77</v>
+        <v>6647.61</v>
       </c>
       <c r="G73">
         <v>4</v>
       </c>
       <c r="H73">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="I73">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="J73">
-        <v>3.9157</v>
+        <v>3.159</v>
       </c>
       <c r="K73">
-        <v>1.9308</v>
+        <v>1.5344</v>
       </c>
       <c r="L73" t="s">
         <v>15</v>
@@ -3671,31 +3668,31 @@
         <v>73</v>
       </c>
       <c r="C74">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="D74">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="E74">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F74">
-        <v>6647.61</v>
+        <v>4778.36</v>
       </c>
       <c r="G74">
         <v>2</v>
       </c>
       <c r="H74">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="I74">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J74">
-        <v>1.399</v>
+        <v>2.0509</v>
       </c>
       <c r="K74">
-        <v>0.7221</v>
+        <v>1.1092</v>
       </c>
       <c r="L74" t="s">
         <v>15</v>
@@ -3715,31 +3712,31 @@
         <v>74</v>
       </c>
       <c r="C75">
-        <v>633</v>
+        <v>614</v>
       </c>
       <c r="D75">
         <v>1211</v>
       </c>
       <c r="E75">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F75">
-        <v>6647.61</v>
+        <v>4778.36</v>
       </c>
       <c r="G75">
         <v>2</v>
       </c>
       <c r="H75">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="I75">
         <v>112</v>
       </c>
       <c r="J75">
-        <v>2.6175</v>
+        <v>3.7042</v>
       </c>
       <c r="K75">
-        <v>1.6848</v>
+        <v>2.3439</v>
       </c>
       <c r="L75" t="s">
         <v>15</v>
@@ -3759,31 +3756,31 @@
         <v>75</v>
       </c>
       <c r="C76">
-        <v>1444</v>
+        <v>1430</v>
       </c>
       <c r="D76">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="E76">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F76">
-        <v>6647.61</v>
+        <v>5541.77</v>
       </c>
       <c r="G76">
         <v>4</v>
       </c>
       <c r="H76">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="I76">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="J76">
-        <v>2.9936</v>
+        <v>4.3668</v>
       </c>
       <c r="K76">
-        <v>1.3689</v>
+        <v>2.2015</v>
       </c>
       <c r="L76" t="s">
         <v>15</v>
@@ -3803,10 +3800,10 @@
         <v>76</v>
       </c>
       <c r="C77">
-        <v>1147</v>
+        <v>1132</v>
       </c>
       <c r="D77">
-        <v>1213</v>
+        <v>1221</v>
       </c>
       <c r="E77">
         <v>92</v>
@@ -3815,19 +3812,19 @@
         <v>6647.61</v>
       </c>
       <c r="G77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H77">
-        <v>155</v>
+        <v>55</v>
       </c>
       <c r="I77">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="J77">
-        <v>2.3317</v>
+        <v>0.8274</v>
       </c>
       <c r="K77">
-        <v>0.9176</v>
+        <v>0.4212</v>
       </c>
       <c r="L77" t="s">
         <v>15</v>
@@ -3847,31 +3844,31 @@
         <v>77</v>
       </c>
       <c r="C78">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="D78">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="E78">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F78">
-        <v>6647.61</v>
+        <v>4778.36</v>
       </c>
       <c r="G78">
         <v>3</v>
       </c>
       <c r="H78">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="I78">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J78">
-        <v>3.7908</v>
+        <v>5.6086</v>
       </c>
       <c r="K78">
-        <v>2.2865</v>
+        <v>3.2229</v>
       </c>
       <c r="L78" t="s">
         <v>15</v>
@@ -3891,31 +3888,31 @@
         <v>78</v>
       </c>
       <c r="C79">
-        <v>905</v>
+        <v>887</v>
       </c>
       <c r="D79">
-        <v>1219</v>
+        <v>1210</v>
       </c>
       <c r="E79">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F79">
-        <v>6647.61</v>
+        <v>4778.36</v>
       </c>
       <c r="G79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H79">
-        <v>37</v>
+        <v>145</v>
       </c>
       <c r="I79">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="J79">
-        <v>0.5566</v>
+        <v>3.0345</v>
       </c>
       <c r="K79">
-        <v>0.5566</v>
+        <v>2.1974</v>
       </c>
       <c r="L79" t="s">
         <v>15</v>
@@ -3935,16 +3932,16 @@
         <v>79</v>
       </c>
       <c r="C80">
-        <v>1287</v>
+        <v>1297</v>
       </c>
       <c r="D80">
-        <v>1222</v>
+        <v>1211</v>
       </c>
       <c r="E80">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="F80">
-        <v>6647.61</v>
+        <v>5026.55</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -3956,10 +3953,10 @@
         <v>29</v>
       </c>
       <c r="J80">
-        <v>0.4362</v>
+        <v>0.5769</v>
       </c>
       <c r="K80">
-        <v>0.4362</v>
+        <v>0.5769</v>
       </c>
       <c r="L80" t="s">
         <v>15</v>
@@ -3979,31 +3976,31 @@
         <v>80</v>
       </c>
       <c r="C81">
-        <v>1557</v>
+        <v>1561</v>
       </c>
       <c r="D81">
-        <v>1227</v>
+        <v>1208</v>
       </c>
       <c r="E81">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F81">
-        <v>6647.61</v>
+        <v>5808.8</v>
       </c>
       <c r="G81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H81">
-        <v>103</v>
+        <v>189</v>
       </c>
       <c r="I81">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="J81">
-        <v>1.5494</v>
+        <v>3.2537</v>
       </c>
       <c r="K81">
-        <v>1.2937</v>
+        <v>1.842</v>
       </c>
       <c r="L81" t="s">
         <v>15</v>
@@ -4023,16 +4020,16 @@
         <v>81</v>
       </c>
       <c r="C82">
-        <v>1720</v>
+        <v>1708</v>
       </c>
       <c r="D82">
-        <v>1287</v>
+        <v>1304</v>
       </c>
       <c r="E82">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F82">
-        <v>5281.02</v>
+        <v>5026.55</v>
       </c>
       <c r="G82">
         <v>1</v>
@@ -4044,10 +4041,10 @@
         <v>40</v>
       </c>
       <c r="J82">
-        <v>0.7574</v>
+        <v>0.7958</v>
       </c>
       <c r="K82">
-        <v>0.7574</v>
+        <v>0.7958</v>
       </c>
       <c r="L82" t="s">
         <v>15</v>
@@ -4067,31 +4064,31 @@
         <v>82</v>
       </c>
       <c r="C83">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D83">
-        <v>1301</v>
+        <v>1308</v>
       </c>
       <c r="E83">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F83">
-        <v>6647.61</v>
+        <v>6082.12</v>
       </c>
       <c r="G83">
         <v>2</v>
       </c>
       <c r="H83">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I83">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J83">
-        <v>3.7307</v>
+        <v>4.094</v>
       </c>
       <c r="K83">
-        <v>3.1139</v>
+        <v>3.4199</v>
       </c>
       <c r="L83" t="s">
         <v>15</v>
@@ -4111,31 +4108,31 @@
         <v>83</v>
       </c>
       <c r="C84">
-        <v>2253</v>
+        <v>2260</v>
       </c>
       <c r="D84">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="E84">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="F84">
-        <v>6647.61</v>
+        <v>5026.55</v>
       </c>
       <c r="G84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H84">
-        <v>40</v>
+        <v>143</v>
       </c>
       <c r="I84">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="J84">
-        <v>0.6017</v>
+        <v>2.8449</v>
       </c>
       <c r="K84">
-        <v>0.6017</v>
+        <v>1.7308</v>
       </c>
       <c r="L84" t="s">
         <v>15</v>
@@ -4158,28 +4155,28 @@
         <v>1294</v>
       </c>
       <c r="D85">
-        <v>1302</v>
+        <v>1311</v>
       </c>
       <c r="E85">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F85">
-        <v>6647.61</v>
+        <v>6361.73</v>
       </c>
       <c r="G85">
         <v>3</v>
       </c>
       <c r="H85">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="I85">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J85">
-        <v>1.1734</v>
+        <v>1.3833</v>
       </c>
       <c r="K85">
-        <v>0.4964</v>
+        <v>0.5502</v>
       </c>
       <c r="L85" t="s">
         <v>15</v>
@@ -4199,16 +4196,16 @@
         <v>85</v>
       </c>
       <c r="C86">
-        <v>1972</v>
+        <v>1980</v>
       </c>
       <c r="D86">
-        <v>1305</v>
+        <v>1300</v>
       </c>
       <c r="E86">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F86">
-        <v>6361.73</v>
+        <v>6647.61</v>
       </c>
       <c r="G86">
         <v>2</v>
@@ -4220,10 +4217,10 @@
         <v>75</v>
       </c>
       <c r="J86">
-        <v>2.2321</v>
+        <v>2.1361</v>
       </c>
       <c r="K86">
-        <v>1.1789</v>
+        <v>1.1282</v>
       </c>
       <c r="L86" t="s">
         <v>15</v>
@@ -4243,10 +4240,10 @@
         <v>86</v>
       </c>
       <c r="C87">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="D87">
-        <v>1306</v>
+        <v>1312</v>
       </c>
       <c r="E87">
         <v>90</v>
@@ -4287,10 +4284,10 @@
         <v>87</v>
       </c>
       <c r="C88">
-        <v>1864</v>
+        <v>1860</v>
       </c>
       <c r="D88">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="E88">
         <v>92</v>
@@ -4302,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="H88">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="I88">
         <v>51</v>
       </c>
       <c r="J88">
-        <v>3.7608</v>
+        <v>3.6855</v>
       </c>
       <c r="K88">
         <v>0.7672</v>
@@ -4331,16 +4328,16 @@
         <v>88</v>
       </c>
       <c r="C89">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="D89">
-        <v>1307</v>
+        <v>1297</v>
       </c>
       <c r="E89">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F89">
-        <v>6361.73</v>
+        <v>6647.61</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -4352,10 +4349,10 @@
         <v>127</v>
       </c>
       <c r="J89">
-        <v>1.9963</v>
+        <v>1.9105</v>
       </c>
       <c r="K89">
-        <v>1.9963</v>
+        <v>1.9105</v>
       </c>
       <c r="L89" t="s">
         <v>15</v>
@@ -4378,28 +4375,28 @@
         <v>624</v>
       </c>
       <c r="D90">
-        <v>1308</v>
+        <v>1302</v>
       </c>
       <c r="E90">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F90">
-        <v>6647.61</v>
+        <v>6361.73</v>
       </c>
       <c r="G90">
         <v>4</v>
       </c>
       <c r="H90">
-        <v>233</v>
+        <v>294</v>
       </c>
       <c r="I90">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="J90">
-        <v>3.505</v>
+        <v>4.6214</v>
       </c>
       <c r="K90">
-        <v>1.6096</v>
+        <v>1.9492</v>
       </c>
       <c r="L90" t="s">
         <v>15</v>
@@ -4419,31 +4416,31 @@
         <v>90</v>
       </c>
       <c r="C91">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D91">
-        <v>1311</v>
+        <v>1296</v>
       </c>
       <c r="E91">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F91">
-        <v>5281.02</v>
+        <v>6647.61</v>
       </c>
       <c r="G91">
         <v>2</v>
       </c>
       <c r="H91">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="I91">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="J91">
-        <v>4.5067</v>
+        <v>3.2493</v>
       </c>
       <c r="K91">
-        <v>3.6735</v>
+        <v>2.6927</v>
       </c>
       <c r="L91" t="s">
         <v>15</v>
@@ -4463,7 +4460,7 @@
         <v>91</v>
       </c>
       <c r="C92">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D92">
         <v>1311</v>
@@ -4507,31 +4504,31 @@
         <v>92</v>
       </c>
       <c r="C93">
-        <v>1423</v>
+        <v>1431</v>
       </c>
       <c r="D93">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="E93">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F93">
-        <v>6647.61</v>
+        <v>6361.73</v>
       </c>
       <c r="G93">
         <v>6</v>
       </c>
       <c r="H93">
-        <v>501</v>
+        <v>562</v>
       </c>
       <c r="I93">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="J93">
-        <v>7.5365</v>
+        <v>8.834099999999999</v>
       </c>
       <c r="K93">
-        <v>2.1511</v>
+        <v>2.2793</v>
       </c>
       <c r="L93" t="s">
         <v>15</v>
@@ -4551,31 +4548,31 @@
         <v>93</v>
       </c>
       <c r="C94">
-        <v>1577</v>
+        <v>1560</v>
       </c>
       <c r="D94">
         <v>1312</v>
       </c>
       <c r="E94">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F94">
-        <v>6361.73</v>
+        <v>6647.61</v>
       </c>
       <c r="G94">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H94">
-        <v>145</v>
+        <v>317</v>
       </c>
       <c r="I94">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="J94">
-        <v>2.2793</v>
+        <v>4.7686</v>
       </c>
       <c r="K94">
-        <v>1.7448</v>
+        <v>2.0007</v>
       </c>
       <c r="L94" t="s">
         <v>15</v>
@@ -4595,31 +4592,31 @@
         <v>94</v>
       </c>
       <c r="C95">
-        <v>488</v>
+        <v>470</v>
       </c>
       <c r="D95">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="E95">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="F95">
-        <v>6647.61</v>
+        <v>4778.36</v>
       </c>
       <c r="G95">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H95">
-        <v>166</v>
+        <v>277</v>
       </c>
       <c r="I95">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J95">
-        <v>2.4971</v>
+        <v>5.797</v>
       </c>
       <c r="K95">
-        <v>1.5795</v>
+        <v>2.1765</v>
       </c>
       <c r="L95" t="s">
         <v>15</v>
@@ -4639,31 +4636,31 @@
         <v>95</v>
       </c>
       <c r="C96">
-        <v>2120</v>
+        <v>2124</v>
       </c>
       <c r="D96">
-        <v>1317</v>
+        <v>1298</v>
       </c>
       <c r="E96">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F96">
-        <v>6361.73</v>
+        <v>6647.61</v>
       </c>
       <c r="G96">
         <v>1</v>
       </c>
       <c r="H96">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="I96">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="J96">
-        <v>0.2987</v>
+        <v>0.9026</v>
       </c>
       <c r="K96">
-        <v>0.2987</v>
+        <v>0.9026</v>
       </c>
       <c r="L96" t="s">
         <v>15</v>
@@ -4683,31 +4680,31 @@
         <v>96</v>
       </c>
       <c r="C97">
-        <v>896</v>
+        <v>879</v>
       </c>
       <c r="D97">
-        <v>1333</v>
+        <v>1396</v>
       </c>
       <c r="E97">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="F97">
-        <v>6361.73</v>
+        <v>3631.68</v>
       </c>
       <c r="G97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H97">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="I97">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J97">
-        <v>2.2321</v>
+        <v>3.0564</v>
       </c>
       <c r="K97">
-        <v>1.3047</v>
+        <v>2.368</v>
       </c>
       <c r="L97" t="s">
         <v>15</v>
@@ -4727,31 +4724,31 @@
         <v>97</v>
       </c>
       <c r="C98">
-        <v>2273</v>
+        <v>2257</v>
       </c>
       <c r="D98">
-        <v>1390</v>
+        <v>1329</v>
       </c>
       <c r="E98">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F98">
-        <v>4071.5</v>
+        <v>3631.68</v>
       </c>
       <c r="G98">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H98">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="I98">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="J98">
-        <v>7.1227</v>
+        <v>0</v>
       </c>
       <c r="K98">
-        <v>5.6981</v>
+        <v>0</v>
       </c>
       <c r="L98" t="s">
         <v>15</v>
@@ -4771,10 +4768,10 @@
         <v>98</v>
       </c>
       <c r="C99">
-        <v>1838</v>
+        <v>1868</v>
       </c>
       <c r="D99">
-        <v>1394</v>
+        <v>1398</v>
       </c>
       <c r="E99">
         <v>92</v>
@@ -4783,16 +4780,16 @@
         <v>6647.61</v>
       </c>
       <c r="G99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H99">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="I99">
         <v>168</v>
       </c>
       <c r="J99">
-        <v>4.0315</v>
+        <v>3.6855</v>
       </c>
       <c r="K99">
         <v>2.5272</v>
@@ -4815,31 +4812,31 @@
         <v>99</v>
       </c>
       <c r="C100">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="D100">
-        <v>1398</v>
+        <v>1410</v>
       </c>
       <c r="E100">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F100">
-        <v>6647.61</v>
+        <v>5541.77</v>
       </c>
       <c r="G100">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H100">
-        <v>339</v>
+        <v>92</v>
       </c>
       <c r="I100">
-        <v>167</v>
+        <v>69</v>
       </c>
       <c r="J100">
-        <v>5.0996</v>
+        <v>1.6601</v>
       </c>
       <c r="K100">
-        <v>2.5122</v>
+        <v>1.2451</v>
       </c>
       <c r="L100" t="s">
         <v>15</v>
@@ -4859,10 +4856,10 @@
         <v>100</v>
       </c>
       <c r="C101">
-        <v>1569</v>
+        <v>1551</v>
       </c>
       <c r="D101">
-        <v>1398</v>
+        <v>1408</v>
       </c>
       <c r="E101">
         <v>92</v>
@@ -4874,16 +4871,16 @@
         <v>2</v>
       </c>
       <c r="H101">
-        <v>80</v>
+        <v>147</v>
       </c>
       <c r="I101">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="J101">
-        <v>1.2034</v>
+        <v>2.2113</v>
       </c>
       <c r="K101">
-        <v>0.8274</v>
+        <v>1.384</v>
       </c>
       <c r="L101" t="s">
         <v>15</v>
@@ -4903,10 +4900,10 @@
         <v>101</v>
       </c>
       <c r="C102">
-        <v>889</v>
+        <v>881</v>
       </c>
       <c r="D102">
-        <v>1399</v>
+        <v>1420</v>
       </c>
       <c r="E102">
         <v>92</v>
@@ -4918,16 +4915,16 @@
         <v>1</v>
       </c>
       <c r="H102">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="I102">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J102">
-        <v>1.0229</v>
+        <v>1.0831</v>
       </c>
       <c r="K102">
-        <v>1.0229</v>
+        <v>1.0831</v>
       </c>
       <c r="L102" t="s">
         <v>15</v>
@@ -4950,28 +4947,28 @@
         <v>1020</v>
       </c>
       <c r="D103">
-        <v>1399</v>
+        <v>1411</v>
       </c>
       <c r="E103">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F103">
-        <v>6647.61</v>
+        <v>5541.77</v>
       </c>
       <c r="G103">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H103">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="I103">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J103">
-        <v>2.1812</v>
+        <v>2.4541</v>
       </c>
       <c r="K103">
-        <v>1.1734</v>
+        <v>1.4977</v>
       </c>
       <c r="L103" t="s">
         <v>15</v>
@@ -4991,31 +4988,31 @@
         <v>103</v>
       </c>
       <c r="C104">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="D104">
-        <v>1399</v>
+        <v>1407</v>
       </c>
       <c r="E104">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="F104">
-        <v>6647.61</v>
+        <v>5281.02</v>
       </c>
       <c r="G104">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H104">
-        <v>184</v>
+        <v>236</v>
       </c>
       <c r="I104">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="J104">
-        <v>2.7679</v>
+        <v>4.4688</v>
       </c>
       <c r="K104">
-        <v>1.5043</v>
+        <v>2.1208</v>
       </c>
       <c r="L104" t="s">
         <v>15</v>
@@ -5035,31 +5032,31 @@
         <v>104</v>
       </c>
       <c r="C105">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D105">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="E105">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F105">
-        <v>6361.73</v>
+        <v>6647.61</v>
       </c>
       <c r="G105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H105">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="I105">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J105">
-        <v>3.0966</v>
+        <v>3.1891</v>
       </c>
       <c r="K105">
-        <v>1.6819</v>
+        <v>1.5946</v>
       </c>
       <c r="L105" t="s">
         <v>15</v>
@@ -5079,31 +5076,31 @@
         <v>105</v>
       </c>
       <c r="C106">
-        <v>2144</v>
+        <v>2132</v>
       </c>
       <c r="D106">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="E106">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="F106">
-        <v>6647.61</v>
+        <v>5026.55</v>
       </c>
       <c r="G106">
         <v>3</v>
       </c>
       <c r="H106">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="I106">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="J106">
-        <v>3.8811</v>
+        <v>5.5903</v>
       </c>
       <c r="K106">
-        <v>3.2192</v>
+        <v>4.4762</v>
       </c>
       <c r="L106" t="s">
         <v>15</v>
@@ -5123,31 +5120,31 @@
         <v>106</v>
       </c>
       <c r="C107">
-        <v>1972</v>
+        <v>1981</v>
       </c>
       <c r="D107">
-        <v>1406</v>
+        <v>1411</v>
       </c>
       <c r="E107">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F107">
-        <v>6647.61</v>
+        <v>6361.73</v>
       </c>
       <c r="G107">
         <v>2</v>
       </c>
       <c r="H107">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="I107">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J107">
-        <v>3.159</v>
+        <v>3.3953</v>
       </c>
       <c r="K107">
-        <v>2.2414</v>
+        <v>2.3736</v>
       </c>
       <c r="L107" t="s">
         <v>15</v>
@@ -5170,13 +5167,13 @@
         <v>462</v>
       </c>
       <c r="D108">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="E108">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F108">
-        <v>5281.02</v>
+        <v>5026.55</v>
       </c>
       <c r="G108">
         <v>3</v>
@@ -5188,10 +5185,10 @@
         <v>122</v>
       </c>
       <c r="J108">
-        <v>3.9386</v>
+        <v>4.138</v>
       </c>
       <c r="K108">
-        <v>2.3102</v>
+        <v>2.4271</v>
       </c>
       <c r="L108" t="s">
         <v>15</v>
@@ -5211,31 +5208,31 @@
         <v>108</v>
       </c>
       <c r="C109">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="D109">
-        <v>1409</v>
+        <v>1408</v>
       </c>
       <c r="E109">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F109">
-        <v>5281.02</v>
+        <v>6361.73</v>
       </c>
       <c r="G109">
         <v>2</v>
       </c>
       <c r="H109">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I109">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="J109">
-        <v>3.0108</v>
+        <v>2.4679</v>
       </c>
       <c r="K109">
-        <v>1.7421</v>
+        <v>1.5876</v>
       </c>
       <c r="L109" t="s">
         <v>15</v>
@@ -5255,31 +5252,31 @@
         <v>109</v>
       </c>
       <c r="C110">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D110">
-        <v>1410</v>
+        <v>1403</v>
       </c>
       <c r="E110">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F110">
-        <v>5281.02</v>
+        <v>6647.61</v>
       </c>
       <c r="G110">
         <v>3</v>
       </c>
       <c r="H110">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="I110">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J110">
-        <v>2.9729</v>
+        <v>2.5423</v>
       </c>
       <c r="K110">
-        <v>1.8557</v>
+        <v>1.4592</v>
       </c>
       <c r="L110" t="s">
         <v>15</v>
@@ -5346,28 +5343,28 @@
         <v>1159</v>
       </c>
       <c r="D112">
-        <v>1429</v>
+        <v>1411</v>
       </c>
       <c r="E112">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F112">
-        <v>6647.61</v>
+        <v>5541.77</v>
       </c>
       <c r="G112">
         <v>2</v>
       </c>
       <c r="H112">
-        <v>155</v>
+        <v>256</v>
       </c>
       <c r="I112">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="J112">
-        <v>2.3317</v>
+        <v>4.6195</v>
       </c>
       <c r="K112">
-        <v>2.091</v>
+        <v>3.4285</v>
       </c>
       <c r="L112" t="s">
         <v>15</v>
@@ -5387,31 +5384,31 @@
         <v>112</v>
       </c>
       <c r="C113">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="D113">
-        <v>1430</v>
+        <v>1410</v>
       </c>
       <c r="E113">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F113">
-        <v>6647.61</v>
+        <v>5541.77</v>
       </c>
       <c r="G113">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H113">
-        <v>276</v>
+        <v>427</v>
       </c>
       <c r="I113">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="J113">
-        <v>4.1519</v>
+        <v>7.7051</v>
       </c>
       <c r="K113">
-        <v>1.1282</v>
+        <v>1.4977</v>
       </c>
       <c r="L113" t="s">
         <v>15</v>
@@ -5431,31 +5428,31 @@
         <v>113</v>
       </c>
       <c r="C114">
-        <v>2286</v>
+        <v>2284</v>
       </c>
       <c r="D114">
-        <v>1490</v>
+        <v>1502</v>
       </c>
       <c r="E114">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="F114">
-        <v>4071.5</v>
+        <v>5281.02</v>
       </c>
       <c r="G114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H114">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="I114">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="J114">
-        <v>1.2035</v>
+        <v>0</v>
       </c>
       <c r="K114">
-        <v>1.2035</v>
+        <v>0</v>
       </c>
       <c r="L114" t="s">
         <v>15</v>
@@ -5475,31 +5472,31 @@
         <v>114</v>
       </c>
       <c r="C115">
-        <v>1721</v>
+        <v>1716</v>
       </c>
       <c r="D115">
-        <v>1499</v>
+        <v>1508</v>
       </c>
       <c r="E115">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F115">
-        <v>6361.73</v>
+        <v>5541.77</v>
       </c>
       <c r="G115">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H115">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="I115">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J115">
-        <v>2.6565</v>
+        <v>3.3924</v>
       </c>
       <c r="K115">
-        <v>2.2321</v>
+        <v>2.5984</v>
       </c>
       <c r="L115" t="s">
         <v>15</v>
@@ -5519,31 +5516,31 @@
         <v>115</v>
       </c>
       <c r="C116">
-        <v>1844</v>
+        <v>1865</v>
       </c>
       <c r="D116">
-        <v>1499</v>
+        <v>1509</v>
       </c>
       <c r="E116">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F116">
-        <v>6647.61</v>
+        <v>6082.12</v>
       </c>
       <c r="G116">
         <v>2</v>
       </c>
       <c r="H116">
-        <v>363</v>
+        <v>326</v>
       </c>
       <c r="I116">
-        <v>323</v>
+        <v>284</v>
       </c>
       <c r="J116">
-        <v>5.4606</v>
+        <v>5.36</v>
       </c>
       <c r="K116">
-        <v>4.8589</v>
+        <v>4.6694</v>
       </c>
       <c r="L116" t="s">
         <v>15</v>
@@ -5563,10 +5560,10 @@
         <v>116</v>
       </c>
       <c r="C117">
-        <v>2137</v>
+        <v>2146</v>
       </c>
       <c r="D117">
-        <v>1500</v>
+        <v>1519</v>
       </c>
       <c r="E117">
         <v>92</v>
@@ -5578,16 +5575,16 @@
         <v>2</v>
       </c>
       <c r="H117">
-        <v>298</v>
+        <v>197</v>
       </c>
       <c r="I117">
-        <v>174</v>
+        <v>126</v>
       </c>
       <c r="J117">
-        <v>4.4828</v>
+        <v>2.9635</v>
       </c>
       <c r="K117">
-        <v>2.6175</v>
+        <v>1.8954</v>
       </c>
       <c r="L117" t="s">
         <v>15</v>
@@ -5607,31 +5604,31 @@
         <v>117</v>
       </c>
       <c r="C118">
-        <v>1591</v>
+        <v>1575</v>
       </c>
       <c r="D118">
-        <v>1503</v>
+        <v>1510</v>
       </c>
       <c r="E118">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F118">
-        <v>6361.73</v>
+        <v>6647.61</v>
       </c>
       <c r="G118">
         <v>4</v>
       </c>
       <c r="H118">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="I118">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J118">
-        <v>2.2635</v>
+        <v>2.0308</v>
       </c>
       <c r="K118">
-        <v>0.7388</v>
+        <v>0.6768999999999999</v>
       </c>
       <c r="L118" t="s">
         <v>15</v>
@@ -5698,28 +5695,28 @@
         <v>454</v>
       </c>
       <c r="D120">
-        <v>1507</v>
+        <v>1512</v>
       </c>
       <c r="E120">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F120">
-        <v>6361.73</v>
+        <v>5281.02</v>
       </c>
       <c r="G120">
         <v>4</v>
       </c>
       <c r="H120">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="I120">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J120">
-        <v>2.5779</v>
+        <v>3.2001</v>
       </c>
       <c r="K120">
-        <v>0.7388</v>
+        <v>0.9468</v>
       </c>
       <c r="L120" t="s">
         <v>15</v>
@@ -5739,31 +5736,31 @@
         <v>120</v>
       </c>
       <c r="C121">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="D121">
-        <v>1508</v>
+        <v>1512</v>
       </c>
       <c r="E121">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F121">
-        <v>6361.73</v>
+        <v>5541.77</v>
       </c>
       <c r="G121">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H121">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="I121">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="J121">
-        <v>5.5174</v>
+        <v>6.2435</v>
       </c>
       <c r="K121">
-        <v>1.3833</v>
+        <v>1.6421</v>
       </c>
       <c r="L121" t="s">
         <v>15</v>
@@ -5783,31 +5780,31 @@
         <v>121</v>
       </c>
       <c r="C122">
-        <v>1990</v>
+        <v>2000</v>
       </c>
       <c r="D122">
-        <v>1510</v>
+        <v>1506</v>
       </c>
       <c r="E122">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F122">
-        <v>6647.61</v>
+        <v>5808.8</v>
       </c>
       <c r="G122">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H122">
-        <v>197</v>
+        <v>243</v>
       </c>
       <c r="I122">
         <v>109</v>
       </c>
       <c r="J122">
-        <v>2.9635</v>
+        <v>4.1833</v>
       </c>
       <c r="K122">
-        <v>1.6397</v>
+        <v>1.8765</v>
       </c>
       <c r="L122" t="s">
         <v>15</v>
@@ -5827,10 +5824,10 @@
         <v>122</v>
       </c>
       <c r="C123">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="D123">
-        <v>1511</v>
+        <v>1495</v>
       </c>
       <c r="E123">
         <v>92</v>
@@ -5842,16 +5839,16 @@
         <v>1</v>
       </c>
       <c r="H123">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I123">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J123">
-        <v>0.2858</v>
+        <v>0.2708</v>
       </c>
       <c r="K123">
-        <v>0.2858</v>
+        <v>0.2708</v>
       </c>
       <c r="L123" t="s">
         <v>15</v>
@@ -5871,31 +5868,31 @@
         <v>123</v>
       </c>
       <c r="C124">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D124">
         <v>1512</v>
       </c>
       <c r="E124">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F124">
-        <v>5541.77</v>
+        <v>5281.02</v>
       </c>
       <c r="G124">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H124">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="I124">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="J124">
-        <v>2.815</v>
+        <v>3.3516</v>
       </c>
       <c r="K124">
-        <v>1.7143</v>
+        <v>1.8557</v>
       </c>
       <c r="L124" t="s">
         <v>15</v>
@@ -5915,31 +5912,31 @@
         <v>124</v>
       </c>
       <c r="C125">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D125">
-        <v>1515</v>
+        <v>1511</v>
       </c>
       <c r="E125">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F125">
-        <v>5541.77</v>
+        <v>6361.73</v>
       </c>
       <c r="G125">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H125">
-        <v>203</v>
+        <v>266</v>
       </c>
       <c r="I125">
-        <v>105</v>
+        <v>147</v>
       </c>
       <c r="J125">
-        <v>3.6631</v>
+        <v>4.1813</v>
       </c>
       <c r="K125">
-        <v>1.8947</v>
+        <v>2.3107</v>
       </c>
       <c r="L125" t="s">
         <v>15</v>
@@ -5959,31 +5956,31 @@
         <v>125</v>
       </c>
       <c r="C126">
-        <v>720</v>
+        <v>738</v>
       </c>
       <c r="D126">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="E126">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F126">
-        <v>6647.61</v>
+        <v>6082.12</v>
       </c>
       <c r="G126">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H126">
-        <v>147</v>
+        <v>207</v>
       </c>
       <c r="I126">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="J126">
-        <v>2.2113</v>
+        <v>3.4034</v>
       </c>
       <c r="K126">
-        <v>0.9026</v>
+        <v>0.855</v>
       </c>
       <c r="L126" t="s">
         <v>15</v>
@@ -6003,31 +6000,31 @@
         <v>126</v>
       </c>
       <c r="C127">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="D127">
-        <v>1531</v>
+        <v>1512</v>
       </c>
       <c r="E127">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F127">
-        <v>6647.61</v>
+        <v>5541.77</v>
       </c>
       <c r="G127">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H127">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="I127">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="J127">
-        <v>5.4155</v>
+        <v>6.3337</v>
       </c>
       <c r="K127">
-        <v>3.3245</v>
+        <v>3.8255</v>
       </c>
       <c r="L127" t="s">
         <v>15</v>
@@ -6050,28 +6047,28 @@
         <v>1439</v>
       </c>
       <c r="D128">
-        <v>1532</v>
+        <v>1511</v>
       </c>
       <c r="E128">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F128">
-        <v>6647.61</v>
+        <v>5541.77</v>
       </c>
       <c r="G128">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H128">
-        <v>166</v>
+        <v>298</v>
       </c>
       <c r="I128">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="J128">
-        <v>2.4971</v>
+        <v>5.3773</v>
       </c>
       <c r="K128">
-        <v>0.5566</v>
+        <v>1.4075</v>
       </c>
       <c r="L128" t="s">
         <v>15</v>
@@ -6094,28 +6091,28 @@
         <v>1299</v>
       </c>
       <c r="D129">
-        <v>1533</v>
+        <v>1512</v>
       </c>
       <c r="E129">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F129">
-        <v>6647.61</v>
+        <v>5541.77</v>
       </c>
       <c r="G129">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H129">
-        <v>113</v>
+        <v>251</v>
       </c>
       <c r="I129">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="J129">
-        <v>1.6999</v>
+        <v>4.5292</v>
       </c>
       <c r="K129">
-        <v>0.5115</v>
+        <v>1.1368</v>
       </c>
       <c r="L129" t="s">
         <v>15</v>
@@ -6135,10 +6132,10 @@
         <v>129</v>
       </c>
       <c r="C130">
-        <v>2169</v>
+        <v>2151</v>
       </c>
       <c r="D130">
-        <v>1608</v>
+        <v>1591</v>
       </c>
       <c r="E130">
         <v>92</v>
@@ -6147,16 +6144,16 @@
         <v>6647.61</v>
       </c>
       <c r="G130">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H130">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="I130">
         <v>229</v>
       </c>
       <c r="J130">
-        <v>3.851</v>
+        <v>4.1519</v>
       </c>
       <c r="K130">
         <v>3.4448</v>
@@ -6179,31 +6176,31 @@
         <v>130</v>
       </c>
       <c r="C131">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="D131">
-        <v>1609</v>
+        <v>1617</v>
       </c>
       <c r="E131">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F131">
-        <v>6647.61</v>
+        <v>6361.73</v>
       </c>
       <c r="G131">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H131">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="I131">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="J131">
-        <v>1.7149</v>
+        <v>1.509</v>
       </c>
       <c r="K131">
-        <v>0.5716</v>
+        <v>0.7544999999999999</v>
       </c>
       <c r="L131" t="s">
         <v>15</v>
@@ -6223,16 +6220,16 @@
         <v>131</v>
       </c>
       <c r="C132">
-        <v>1864</v>
+        <v>1870</v>
       </c>
       <c r="D132">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="E132">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F132">
-        <v>6361.73</v>
+        <v>5808.8</v>
       </c>
       <c r="G132">
         <v>5</v>
@@ -6241,13 +6238,13 @@
         <v>363</v>
       </c>
       <c r="I132">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="J132">
-        <v>5.706</v>
+        <v>6.2491</v>
       </c>
       <c r="K132">
-        <v>2.8609</v>
+        <v>3.202</v>
       </c>
       <c r="L132" t="s">
         <v>15</v>
@@ -6267,31 +6264,31 @@
         <v>132</v>
       </c>
       <c r="C133">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="D133">
-        <v>1613</v>
+        <v>1629</v>
       </c>
       <c r="E133">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F133">
-        <v>6361.73</v>
+        <v>6647.61</v>
       </c>
       <c r="G133">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H133">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="I133">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J133">
-        <v>5.0772</v>
+        <v>4.904</v>
       </c>
       <c r="K133">
-        <v>1.3047</v>
+        <v>1.3238</v>
       </c>
       <c r="L133" t="s">
         <v>15</v>
@@ -6311,16 +6308,16 @@
         <v>133</v>
       </c>
       <c r="C134">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="D134">
-        <v>1614</v>
+        <v>1607</v>
       </c>
       <c r="E134">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F134">
-        <v>5541.77</v>
+        <v>6647.61</v>
       </c>
       <c r="G134">
         <v>2</v>
@@ -6332,10 +6329,10 @@
         <v>50</v>
       </c>
       <c r="J134">
-        <v>1.4977</v>
+        <v>1.2486</v>
       </c>
       <c r="K134">
-        <v>0.9022</v>
+        <v>0.7522</v>
       </c>
       <c r="L134" t="s">
         <v>15</v>
@@ -6355,31 +6352,31 @@
         <v>134</v>
       </c>
       <c r="C135">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="D135">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="E135">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F135">
-        <v>5808.8</v>
+        <v>6647.61</v>
       </c>
       <c r="G135">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H135">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="I135">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="J135">
-        <v>3.6152</v>
+        <v>2.4971</v>
       </c>
       <c r="K135">
-        <v>1.1362</v>
+        <v>0.9628</v>
       </c>
       <c r="L135" t="s">
         <v>15</v>
@@ -6399,31 +6396,31 @@
         <v>135</v>
       </c>
       <c r="C136">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="D136">
-        <v>1616</v>
+        <v>1607</v>
       </c>
       <c r="E136">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F136">
-        <v>5541.77</v>
+        <v>6647.61</v>
       </c>
       <c r="G136">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H136">
-        <v>282</v>
+        <v>211</v>
       </c>
       <c r="I136">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="J136">
-        <v>5.0886</v>
+        <v>3.1741</v>
       </c>
       <c r="K136">
-        <v>1.7143</v>
+        <v>1.384</v>
       </c>
       <c r="L136" t="s">
         <v>15</v>
@@ -6443,31 +6440,31 @@
         <v>136</v>
       </c>
       <c r="C137">
-        <v>871</v>
+        <v>876</v>
       </c>
       <c r="D137">
-        <v>1616</v>
+        <v>1607</v>
       </c>
       <c r="E137">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F137">
-        <v>6361.73</v>
+        <v>6647.61</v>
       </c>
       <c r="G137">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H137">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="I137">
-        <v>61</v>
+        <v>96</v>
       </c>
       <c r="J137">
-        <v>5.6746</v>
+        <v>5.235</v>
       </c>
       <c r="K137">
-        <v>0.9589</v>
+        <v>1.4441</v>
       </c>
       <c r="L137" t="s">
         <v>15</v>
@@ -6487,31 +6484,31 @@
         <v>137</v>
       </c>
       <c r="C138">
-        <v>1735</v>
+        <v>1722</v>
       </c>
       <c r="D138">
-        <v>1619</v>
+        <v>1609</v>
       </c>
       <c r="E138">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F138">
-        <v>6361.73</v>
+        <v>5808.8</v>
       </c>
       <c r="G138">
         <v>2</v>
       </c>
       <c r="H138">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I138">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="J138">
-        <v>2.2164</v>
+        <v>2.3757</v>
       </c>
       <c r="K138">
-        <v>1.3047</v>
+        <v>1.4977</v>
       </c>
       <c r="L138" t="s">
         <v>15</v>
@@ -6531,31 +6528,31 @@
         <v>138</v>
       </c>
       <c r="C139">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="D139">
-        <v>1620</v>
+        <v>1602</v>
       </c>
       <c r="E139">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F139">
-        <v>6361.73</v>
+        <v>6647.61</v>
       </c>
       <c r="G139">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H139">
-        <v>400</v>
+        <v>267</v>
       </c>
       <c r="I139">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J139">
-        <v>6.2876</v>
+        <v>4.0165</v>
       </c>
       <c r="K139">
-        <v>1.2418</v>
+        <v>1.1734</v>
       </c>
       <c r="L139" t="s">
         <v>15</v>
@@ -6575,31 +6572,31 @@
         <v>139</v>
       </c>
       <c r="C140">
-        <v>2022</v>
+        <v>2011</v>
       </c>
       <c r="D140">
-        <v>1620</v>
+        <v>1610</v>
       </c>
       <c r="E140">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F140">
-        <v>6647.61</v>
+        <v>5541.77</v>
       </c>
       <c r="G140">
         <v>2</v>
       </c>
       <c r="H140">
-        <v>329</v>
+        <v>372</v>
       </c>
       <c r="I140">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="J140">
-        <v>4.9491</v>
+        <v>6.7127</v>
       </c>
       <c r="K140">
-        <v>4.3775</v>
+        <v>5.2871</v>
       </c>
       <c r="L140" t="s">
         <v>15</v>
@@ -6622,28 +6619,28 @@
         <v>1016</v>
       </c>
       <c r="D141">
-        <v>1632</v>
+        <v>1616</v>
       </c>
       <c r="E141">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F141">
-        <v>6647.61</v>
+        <v>5541.77</v>
       </c>
       <c r="G141">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H141">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="I141">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="J141">
-        <v>5.0093</v>
+        <v>6.2976</v>
       </c>
       <c r="K141">
-        <v>2.7529</v>
+        <v>3.8977</v>
       </c>
       <c r="L141" t="s">
         <v>15</v>
@@ -6666,28 +6663,28 @@
         <v>1441</v>
       </c>
       <c r="D142">
-        <v>1634</v>
+        <v>1615</v>
       </c>
       <c r="E142">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F142">
-        <v>6647.61</v>
+        <v>5541.77</v>
       </c>
       <c r="G142">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H142">
-        <v>229</v>
+        <v>356</v>
       </c>
       <c r="I142">
-        <v>177</v>
+        <v>238</v>
       </c>
       <c r="J142">
-        <v>3.4448</v>
+        <v>6.4239</v>
       </c>
       <c r="K142">
-        <v>2.6626</v>
+        <v>4.2947</v>
       </c>
       <c r="L142" t="s">
         <v>15</v>
@@ -6707,31 +6704,31 @@
         <v>142</v>
       </c>
       <c r="C143">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="D143">
-        <v>1638</v>
+        <v>1617</v>
       </c>
       <c r="E143">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F143">
-        <v>6647.61</v>
+        <v>5541.77</v>
       </c>
       <c r="G143">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H143">
-        <v>133</v>
+        <v>257</v>
       </c>
       <c r="I143">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="J143">
-        <v>2.0007</v>
+        <v>4.6375</v>
       </c>
       <c r="K143">
-        <v>0.8424</v>
+        <v>2.1834</v>
       </c>
       <c r="L143" t="s">
         <v>15</v>
@@ -6751,31 +6748,31 @@
         <v>143</v>
       </c>
       <c r="C144">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="D144">
-        <v>1638</v>
+        <v>1616</v>
       </c>
       <c r="E144">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F144">
-        <v>6647.61</v>
+        <v>5808.8</v>
       </c>
       <c r="G144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I144">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J144">
-        <v>0</v>
+        <v>0.4476</v>
       </c>
       <c r="K144">
-        <v>0</v>
+        <v>0.4476</v>
       </c>
       <c r="L144" t="s">
         <v>15</v>
@@ -6839,10 +6836,10 @@
         <v>145</v>
       </c>
       <c r="C146">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="D146">
-        <v>1711</v>
+        <v>1714</v>
       </c>
       <c r="E146">
         <v>90</v>
@@ -6854,13 +6851,13 @@
         <v>3</v>
       </c>
       <c r="H146">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I146">
         <v>33</v>
       </c>
       <c r="J146">
-        <v>1.1789</v>
+        <v>1.289</v>
       </c>
       <c r="K146">
         <v>0.5187</v>
@@ -6883,10 +6880,10 @@
         <v>146</v>
       </c>
       <c r="C147">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="D147">
-        <v>1714</v>
+        <v>1728</v>
       </c>
       <c r="E147">
         <v>92</v>
@@ -6895,16 +6892,16 @@
         <v>6647.61</v>
       </c>
       <c r="G147">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H147">
-        <v>306</v>
+        <v>253</v>
       </c>
       <c r="I147">
         <v>184</v>
       </c>
       <c r="J147">
-        <v>4.6032</v>
+        <v>3.8059</v>
       </c>
       <c r="K147">
         <v>2.7679</v>
@@ -6927,31 +6924,31 @@
         <v>147</v>
       </c>
       <c r="C148">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="D148">
-        <v>1715</v>
+        <v>1722</v>
       </c>
       <c r="E148">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F148">
-        <v>6647.61</v>
+        <v>6082.12</v>
       </c>
       <c r="G148">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H148">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I148">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J148">
-        <v>2.6626</v>
+        <v>2.9431</v>
       </c>
       <c r="K148">
-        <v>0.9628</v>
+        <v>1.0687</v>
       </c>
       <c r="L148" t="s">
         <v>15</v>
@@ -6971,10 +6968,10 @@
         <v>148</v>
       </c>
       <c r="C149">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="D149">
-        <v>1716</v>
+        <v>1718</v>
       </c>
       <c r="E149">
         <v>90</v>
@@ -6986,13 +6983,13 @@
         <v>5</v>
       </c>
       <c r="H149">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="I149">
         <v>68</v>
       </c>
       <c r="J149">
-        <v>3.5839</v>
+        <v>3.804</v>
       </c>
       <c r="K149">
         <v>1.0689</v>
@@ -7015,31 +7012,31 @@
         <v>149</v>
       </c>
       <c r="C150">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="D150">
-        <v>1717</v>
+        <v>1739</v>
       </c>
       <c r="E150">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F150">
-        <v>6361.73</v>
+        <v>6647.61</v>
       </c>
       <c r="G150">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H150">
-        <v>357</v>
+        <v>291</v>
       </c>
       <c r="I150">
         <v>70</v>
       </c>
       <c r="J150">
-        <v>5.6117</v>
+        <v>4.3775</v>
       </c>
       <c r="K150">
-        <v>1.1003</v>
+        <v>1.053</v>
       </c>
       <c r="L150" t="s">
         <v>15</v>
@@ -7059,31 +7056,31 @@
         <v>150</v>
       </c>
       <c r="C151">
-        <v>2180</v>
+        <v>2164</v>
       </c>
       <c r="D151">
-        <v>1718</v>
+        <v>1715</v>
       </c>
       <c r="E151">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F151">
-        <v>6647.61</v>
+        <v>5808.8</v>
       </c>
       <c r="G151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H151">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="I151">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="J151">
-        <v>1.8804</v>
+        <v>3.1848</v>
       </c>
       <c r="K151">
-        <v>1.8804</v>
+        <v>2.3929</v>
       </c>
       <c r="L151" t="s">
         <v>15</v>
@@ -7103,31 +7100,31 @@
         <v>151</v>
       </c>
       <c r="C152">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="D152">
-        <v>1719</v>
+        <v>1722</v>
       </c>
       <c r="E152">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F152">
-        <v>6082.12</v>
+        <v>6647.61</v>
       </c>
       <c r="G152">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H152">
-        <v>363</v>
+        <v>425</v>
       </c>
       <c r="I152">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J152">
-        <v>5.9683</v>
+        <v>6.3933</v>
       </c>
       <c r="K152">
-        <v>1.8743</v>
+        <v>1.6999</v>
       </c>
       <c r="L152" t="s">
         <v>15</v>
@@ -7147,31 +7144,31 @@
         <v>152</v>
       </c>
       <c r="C153">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="D153">
-        <v>1721</v>
+        <v>1726</v>
       </c>
       <c r="E153">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="F153">
-        <v>5281.02</v>
+        <v>6647.61</v>
       </c>
       <c r="G153">
         <v>3</v>
       </c>
       <c r="H153">
-        <v>152</v>
+        <v>127</v>
       </c>
       <c r="I153">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="J153">
-        <v>2.8782</v>
+        <v>1.9105</v>
       </c>
       <c r="K153">
-        <v>1.1172</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="L153" t="s">
         <v>15</v>
@@ -7235,10 +7232,10 @@
         <v>154</v>
       </c>
       <c r="C155">
-        <v>1855</v>
+        <v>1861</v>
       </c>
       <c r="D155">
-        <v>1727</v>
+        <v>1723</v>
       </c>
       <c r="E155">
         <v>92</v>
@@ -7247,19 +7244,19 @@
         <v>6647.61</v>
       </c>
       <c r="G155">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H155">
-        <v>156</v>
+        <v>282</v>
       </c>
       <c r="I155">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J155">
-        <v>2.3467</v>
+        <v>4.2421</v>
       </c>
       <c r="K155">
-        <v>2.3467</v>
+        <v>2.3918</v>
       </c>
       <c r="L155" t="s">
         <v>15</v>
@@ -7279,31 +7276,31 @@
         <v>155</v>
       </c>
       <c r="C156">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="D156">
-        <v>1729</v>
+        <v>1720</v>
       </c>
       <c r="E156">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F156">
-        <v>6361.73</v>
+        <v>6647.61</v>
       </c>
       <c r="G156">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H156">
-        <v>187</v>
+        <v>264</v>
       </c>
       <c r="I156">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="J156">
-        <v>2.9395</v>
+        <v>3.9714</v>
       </c>
       <c r="K156">
-        <v>0.9746</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="L156" t="s">
         <v>15</v>
@@ -7323,10 +7320,10 @@
         <v>156</v>
       </c>
       <c r="C157">
-        <v>718</v>
+        <v>734</v>
       </c>
       <c r="D157">
-        <v>1730</v>
+        <v>1726</v>
       </c>
       <c r="E157">
         <v>92</v>
@@ -7338,16 +7335,16 @@
         <v>7</v>
       </c>
       <c r="H157">
-        <v>238</v>
+        <v>277</v>
       </c>
       <c r="I157">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="J157">
-        <v>3.5802</v>
+        <v>4.1669</v>
       </c>
       <c r="K157">
-        <v>0.7371</v>
+        <v>1.384</v>
       </c>
       <c r="L157" t="s">
         <v>15</v>
@@ -7499,10 +7496,10 @@
         <v>160</v>
       </c>
       <c r="C161">
-        <v>1307</v>
+        <v>1294</v>
       </c>
       <c r="D161">
-        <v>1813</v>
+        <v>1830</v>
       </c>
       <c r="E161">
         <v>92</v>
@@ -7511,16 +7508,16 @@
         <v>6647.61</v>
       </c>
       <c r="G161">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H161">
-        <v>139</v>
+        <v>189</v>
       </c>
       <c r="I161">
         <v>65</v>
       </c>
       <c r="J161">
-        <v>2.091</v>
+        <v>2.8431</v>
       </c>
       <c r="K161">
         <v>0.9778</v>
@@ -7543,31 +7540,31 @@
         <v>161</v>
       </c>
       <c r="C162">
-        <v>2089</v>
+        <v>2151</v>
       </c>
       <c r="D162">
-        <v>1815</v>
+        <v>1827</v>
       </c>
       <c r="E162">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F162">
-        <v>4071.5</v>
+        <v>3631.68</v>
       </c>
       <c r="G162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H162">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="I162">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J162">
-        <v>1.7193</v>
+        <v>0</v>
       </c>
       <c r="K162">
-        <v>1.7193</v>
+        <v>0</v>
       </c>
       <c r="L162" t="s">
         <v>15</v>
@@ -7587,31 +7584,31 @@
         <v>162</v>
       </c>
       <c r="C163">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D163">
-        <v>1823</v>
+        <v>1830</v>
       </c>
       <c r="E163">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F163">
-        <v>6647.61</v>
+        <v>6082.12</v>
       </c>
       <c r="G163">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H163">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="I163">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J163">
-        <v>3.4599</v>
+        <v>4.2748</v>
       </c>
       <c r="K163">
-        <v>1.038</v>
+        <v>1.1509</v>
       </c>
       <c r="L163" t="s">
         <v>15</v>
@@ -7631,31 +7628,31 @@
         <v>163</v>
       </c>
       <c r="C164">
-        <v>1869</v>
+        <v>1884</v>
       </c>
       <c r="D164">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="E164">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F164">
-        <v>6647.61</v>
+        <v>6082.12</v>
       </c>
       <c r="G164">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H164">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="I164">
         <v>182</v>
       </c>
       <c r="J164">
-        <v>4.8438</v>
+        <v>5.7052</v>
       </c>
       <c r="K164">
-        <v>2.7378</v>
+        <v>2.9924</v>
       </c>
       <c r="L164" t="s">
         <v>15</v>
@@ -7675,10 +7672,10 @@
         <v>164</v>
       </c>
       <c r="C165">
-        <v>2193</v>
+        <v>2184</v>
       </c>
       <c r="D165">
-        <v>1825</v>
+        <v>1837</v>
       </c>
       <c r="E165">
         <v>92</v>
@@ -7687,19 +7684,19 @@
         <v>6647.61</v>
       </c>
       <c r="G165">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H165">
-        <v>330</v>
+        <v>253</v>
       </c>
       <c r="I165">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J165">
-        <v>4.9642</v>
+        <v>3.8059</v>
       </c>
       <c r="K165">
-        <v>2.9936</v>
+        <v>3.0086</v>
       </c>
       <c r="L165" t="s">
         <v>15</v>
@@ -7719,31 +7716,31 @@
         <v>165</v>
       </c>
       <c r="C166">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D166">
-        <v>1826</v>
+        <v>1830</v>
       </c>
       <c r="E166">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F166">
-        <v>6361.73</v>
+        <v>5808.8</v>
       </c>
       <c r="G166">
         <v>7</v>
       </c>
       <c r="H166">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="I166">
         <v>69</v>
       </c>
       <c r="J166">
-        <v>4.3542</v>
+        <v>4.8547</v>
       </c>
       <c r="K166">
-        <v>1.0846</v>
+        <v>1.1879</v>
       </c>
       <c r="L166" t="s">
         <v>15</v>
@@ -7807,31 +7804,31 @@
         <v>167</v>
       </c>
       <c r="C168">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="D168">
         <v>1829</v>
       </c>
       <c r="E168">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="F168">
-        <v>5541.77</v>
+        <v>6647.61</v>
       </c>
       <c r="G168">
         <v>9</v>
       </c>
       <c r="H168">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="I168">
         <v>91</v>
       </c>
       <c r="J168">
-        <v>7.8675</v>
+        <v>6.7092</v>
       </c>
       <c r="K168">
-        <v>1.6421</v>
+        <v>1.3689</v>
       </c>
       <c r="L168" t="s">
         <v>15</v>
@@ -7851,31 +7848,31 @@
         <v>168</v>
       </c>
       <c r="C169">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="D169">
-        <v>1831</v>
+        <v>1834</v>
       </c>
       <c r="E169">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F169">
-        <v>6082.12</v>
+        <v>6647.61</v>
       </c>
       <c r="G169">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H169">
-        <v>305</v>
+        <v>394</v>
       </c>
       <c r="I169">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="J169">
-        <v>5.0147</v>
+        <v>5.9269</v>
       </c>
       <c r="K169">
-        <v>1.0029</v>
+        <v>1.1583</v>
       </c>
       <c r="L169" t="s">
         <v>15</v>
@@ -7939,31 +7936,31 @@
         <v>170</v>
       </c>
       <c r="C171">
-        <v>1752</v>
+        <v>1739</v>
       </c>
       <c r="D171">
-        <v>1831</v>
+        <v>1827</v>
       </c>
       <c r="E171">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F171">
-        <v>6647.61</v>
+        <v>5808.8</v>
       </c>
       <c r="G171">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H171">
-        <v>214</v>
+        <v>146</v>
       </c>
       <c r="I171">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="J171">
-        <v>3.2192</v>
+        <v>2.5134</v>
       </c>
       <c r="K171">
-        <v>1.0681</v>
+        <v>0.9813</v>
       </c>
       <c r="L171" t="s">
         <v>15</v>
@@ -7983,31 +7980,31 @@
         <v>171</v>
       </c>
       <c r="C172">
-        <v>2027</v>
+        <v>2024</v>
       </c>
       <c r="D172">
         <v>1831</v>
       </c>
       <c r="E172">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F172">
-        <v>5026.55</v>
+        <v>6647.61</v>
       </c>
       <c r="G172">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H172">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="I172">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="J172">
-        <v>2.1884</v>
+        <v>1.3539</v>
       </c>
       <c r="K172">
-        <v>2.1884</v>
+        <v>1.0681</v>
       </c>
       <c r="L172" t="s">
         <v>15</v>
@@ -8027,10 +8024,10 @@
         <v>172</v>
       </c>
       <c r="C173">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="D173">
-        <v>1838</v>
+        <v>1826</v>
       </c>
       <c r="E173">
         <v>92</v>
@@ -8042,13 +8039,13 @@
         <v>7</v>
       </c>
       <c r="H173">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="I173">
         <v>80</v>
       </c>
       <c r="J173">
-        <v>4.0315</v>
+        <v>3.9714</v>
       </c>
       <c r="K173">
         <v>1.2034</v>
@@ -8115,10 +8112,10 @@
         <v>174</v>
       </c>
       <c r="C175">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D175">
-        <v>1928</v>
+        <v>1936</v>
       </c>
       <c r="E175">
         <v>92</v>
@@ -8159,31 +8156,31 @@
         <v>175</v>
       </c>
       <c r="C176">
-        <v>2083</v>
+        <v>2041</v>
       </c>
       <c r="D176">
-        <v>1929</v>
+        <v>1939</v>
       </c>
       <c r="E176">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F176">
-        <v>4778.36</v>
+        <v>5281.02</v>
       </c>
       <c r="G176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H176">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I176">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J176">
-        <v>0</v>
+        <v>0.3598</v>
       </c>
       <c r="K176">
-        <v>0</v>
+        <v>0.3598</v>
       </c>
       <c r="L176" t="s">
         <v>15</v>
@@ -8203,10 +8200,10 @@
         <v>176</v>
       </c>
       <c r="C177">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D177">
-        <v>1930</v>
+        <v>1949</v>
       </c>
       <c r="E177">
         <v>92</v>
@@ -8215,16 +8212,16 @@
         <v>6647.61</v>
       </c>
       <c r="G177">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H177">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="I177">
         <v>51</v>
       </c>
       <c r="J177">
-        <v>1.4291</v>
+        <v>1.745</v>
       </c>
       <c r="K177">
         <v>0.7672</v>
@@ -8247,31 +8244,31 @@
         <v>177</v>
       </c>
       <c r="C178">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="D178">
-        <v>1930</v>
+        <v>1939</v>
       </c>
       <c r="E178">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F178">
-        <v>6647.61</v>
+        <v>6361.73</v>
       </c>
       <c r="G178">
         <v>6</v>
       </c>
       <c r="H178">
-        <v>221</v>
+        <v>264</v>
       </c>
       <c r="I178">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="J178">
-        <v>3.3245</v>
+        <v>4.1498</v>
       </c>
       <c r="K178">
-        <v>1.1583</v>
+        <v>1.8391</v>
       </c>
       <c r="L178" t="s">
         <v>15</v>
@@ -8291,31 +8288,31 @@
         <v>178</v>
       </c>
       <c r="C179">
-        <v>1889</v>
+        <v>1891</v>
       </c>
       <c r="D179">
-        <v>1934</v>
+        <v>1939</v>
       </c>
       <c r="E179">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F179">
-        <v>6647.61</v>
+        <v>6082.12</v>
       </c>
       <c r="G179">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H179">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="I179">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="J179">
-        <v>4.8138</v>
+        <v>5.4422</v>
       </c>
       <c r="K179">
-        <v>2.4821</v>
+        <v>2.4662</v>
       </c>
       <c r="L179" t="s">
         <v>15</v>
@@ -8423,10 +8420,10 @@
         <v>181</v>
       </c>
       <c r="C182">
-        <v>2170</v>
+        <v>2186</v>
       </c>
       <c r="D182">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="E182">
         <v>92</v>
@@ -8470,7 +8467,7 @@
         <v>2026</v>
       </c>
       <c r="D183">
-        <v>1938</v>
+        <v>1919</v>
       </c>
       <c r="E183">
         <v>92</v>
@@ -8511,31 +8508,31 @@
         <v>183</v>
       </c>
       <c r="C184">
-        <v>1155</v>
+        <v>1164</v>
       </c>
       <c r="D184">
-        <v>1939</v>
+        <v>1951</v>
       </c>
       <c r="E184">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F184">
-        <v>5808.8</v>
+        <v>6647.61</v>
       </c>
       <c r="G184">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H184">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I184">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="J184">
-        <v>4.2694</v>
+        <v>3.8059</v>
       </c>
       <c r="K184">
-        <v>1.0501</v>
+        <v>1.5344</v>
       </c>
       <c r="L184" t="s">
         <v>15</v>
@@ -8555,31 +8552,31 @@
         <v>184</v>
       </c>
       <c r="C185">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="D185">
-        <v>1939</v>
+        <v>1944</v>
       </c>
       <c r="E185">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F185">
-        <v>5541.77</v>
+        <v>6361.73</v>
       </c>
       <c r="G185">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H185">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="I185">
         <v>47</v>
       </c>
       <c r="J185">
-        <v>1.3714</v>
+        <v>1.399</v>
       </c>
       <c r="K185">
-        <v>0.8481</v>
+        <v>0.7388</v>
       </c>
       <c r="L185" t="s">
         <v>15</v>
@@ -8599,31 +8596,31 @@
         <v>185</v>
       </c>
       <c r="C186">
-        <v>1450</v>
+        <v>1453</v>
       </c>
       <c r="D186">
-        <v>1940</v>
+        <v>1943</v>
       </c>
       <c r="E186">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F186">
-        <v>5541.77</v>
+        <v>6082.12</v>
       </c>
       <c r="G186">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H186">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="I186">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="J186">
-        <v>3.7533</v>
+        <v>3.6994</v>
       </c>
       <c r="K186">
-        <v>1.209</v>
+        <v>0.9701</v>
       </c>
       <c r="L186" t="s">
         <v>15</v>
@@ -8687,31 +8684,31 @@
         <v>187</v>
       </c>
       <c r="C188">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="D188">
         <v>1940</v>
       </c>
       <c r="E188">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F188">
-        <v>5541.77</v>
+        <v>5808.8</v>
       </c>
       <c r="G188">
         <v>3</v>
       </c>
       <c r="H188">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="I188">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="J188">
-        <v>1.4075</v>
+        <v>1.6354</v>
       </c>
       <c r="K188">
-        <v>0.6135</v>
+        <v>0.723</v>
       </c>
       <c r="L188" t="s">
         <v>15</v>
@@ -8731,31 +8728,31 @@
         <v>188</v>
       </c>
       <c r="C189">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="D189">
-        <v>1941</v>
+        <v>1950</v>
       </c>
       <c r="E189">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F189">
-        <v>5808.8</v>
+        <v>6647.61</v>
       </c>
       <c r="G189">
         <v>7</v>
       </c>
       <c r="H189">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="I189">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="J189">
-        <v>5.0269</v>
+        <v>4.0014</v>
       </c>
       <c r="K189">
-        <v>1.3084</v>
+        <v>0.9628</v>
       </c>
       <c r="L189" t="s">
         <v>15</v>
@@ -8775,31 +8772,31 @@
         <v>189</v>
       </c>
       <c r="C190">
-        <v>324</v>
+        <v>274</v>
       </c>
       <c r="D190">
-        <v>1944</v>
+        <v>1940</v>
       </c>
       <c r="E190">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F190">
-        <v>6647.61</v>
+        <v>5541.77</v>
       </c>
       <c r="G190">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H190">
-        <v>0</v>
+        <v>343</v>
       </c>
       <c r="I190">
-        <v>0</v>
+        <v>159</v>
       </c>
       <c r="J190">
-        <v>0</v>
+        <v>6.1894</v>
       </c>
       <c r="K190">
-        <v>0</v>
+        <v>2.8691</v>
       </c>
       <c r="L190" t="s">
         <v>15</v>
@@ -8819,10 +8816,10 @@
         <v>190</v>
       </c>
       <c r="C191">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="D191">
-        <v>2042</v>
+        <v>2050</v>
       </c>
       <c r="E191">
         <v>92</v>
@@ -8831,19 +8828,19 @@
         <v>6647.61</v>
       </c>
       <c r="G191">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H191">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="I191">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J191">
-        <v>2.6626</v>
+        <v>3.0086</v>
       </c>
       <c r="K191">
-        <v>1.1433</v>
+        <v>1.1884</v>
       </c>
       <c r="L191" t="s">
         <v>15</v>
@@ -8863,10 +8860,10 @@
         <v>191</v>
       </c>
       <c r="C192">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="D192">
-        <v>2047</v>
+        <v>2051</v>
       </c>
       <c r="E192">
         <v>92</v>
@@ -8875,16 +8872,16 @@
         <v>6647.61</v>
       </c>
       <c r="G192">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H192">
-        <v>248</v>
+        <v>290</v>
       </c>
       <c r="I192">
         <v>182</v>
       </c>
       <c r="J192">
-        <v>3.7307</v>
+        <v>4.3625</v>
       </c>
       <c r="K192">
         <v>2.7378</v>
@@ -8907,10 +8904,10 @@
         <v>192</v>
       </c>
       <c r="C193">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="D193">
-        <v>2048</v>
+        <v>2059</v>
       </c>
       <c r="E193">
         <v>92</v>
@@ -8919,16 +8916,16 @@
         <v>6647.61</v>
       </c>
       <c r="G193">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H193">
-        <v>398</v>
+        <v>355</v>
       </c>
       <c r="I193">
         <v>170</v>
       </c>
       <c r="J193">
-        <v>5.9871</v>
+        <v>5.3403</v>
       </c>
       <c r="K193">
         <v>2.5573</v>
@@ -8995,31 +8992,31 @@
         <v>194</v>
       </c>
       <c r="C195">
-        <v>1898</v>
+        <v>1892</v>
       </c>
       <c r="D195">
-        <v>2051</v>
+        <v>2055</v>
       </c>
       <c r="E195">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F195">
-        <v>5808.8</v>
+        <v>6361.73</v>
       </c>
       <c r="G195">
         <v>4</v>
       </c>
       <c r="H195">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="I195">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="J195">
-        <v>5.9393</v>
+        <v>5.1558</v>
       </c>
       <c r="K195">
-        <v>2.1519</v>
+        <v>1.9177</v>
       </c>
       <c r="L195" t="s">
         <v>15</v>
@@ -9039,31 +9036,31 @@
         <v>195</v>
       </c>
       <c r="C196">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="D196">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="E196">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F196">
-        <v>5808.8</v>
+        <v>6647.61</v>
       </c>
       <c r="G196">
         <v>6</v>
       </c>
       <c r="H196">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="I196">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J196">
-        <v>5.0269</v>
+        <v>4.2421</v>
       </c>
       <c r="K196">
-        <v>2.0142</v>
+        <v>1.745</v>
       </c>
       <c r="L196" t="s">
         <v>15</v>
@@ -9083,31 +9080,31 @@
         <v>196</v>
       </c>
       <c r="C197">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D197">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="E197">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F197">
-        <v>6082.12</v>
+        <v>6647.61</v>
       </c>
       <c r="G197">
         <v>7</v>
       </c>
       <c r="H197">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I197">
         <v>75</v>
       </c>
       <c r="J197">
-        <v>4.3077</v>
+        <v>3.9563</v>
       </c>
       <c r="K197">
-        <v>1.2331</v>
+        <v>1.1282</v>
       </c>
       <c r="L197" t="s">
         <v>15</v>
@@ -9130,28 +9127,28 @@
         <v>1155</v>
       </c>
       <c r="D198">
-        <v>2054</v>
+        <v>2048</v>
       </c>
       <c r="E198">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="F198">
-        <v>5808.8</v>
+        <v>6647.61</v>
       </c>
       <c r="G198">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H198">
-        <v>237</v>
+        <v>162</v>
       </c>
       <c r="I198">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J198">
-        <v>4.08</v>
+        <v>2.437</v>
       </c>
       <c r="K198">
-        <v>0.9296</v>
+        <v>0.8274</v>
       </c>
       <c r="L198" t="s">
         <v>15</v>
@@ -9303,31 +9300,31 @@
         <v>201</v>
       </c>
       <c r="C202">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="D202">
-        <v>2055</v>
+        <v>2045</v>
       </c>
       <c r="E202">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F202">
-        <v>6082.12</v>
+        <v>6647.61</v>
       </c>
       <c r="G202">
         <v>2</v>
       </c>
       <c r="H202">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I202">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J202">
-        <v>1.2002</v>
+        <v>1.053</v>
       </c>
       <c r="K202">
-        <v>0.8714</v>
+        <v>0.7522</v>
       </c>
       <c r="L202" t="s">
         <v>15</v>
@@ -9391,10 +9388,10 @@
         <v>203</v>
       </c>
       <c r="C204">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="D204">
-        <v>2059</v>
+        <v>2065</v>
       </c>
       <c r="E204">
         <v>92</v>
@@ -9406,16 +9403,16 @@
         <v>6</v>
       </c>
       <c r="H204">
-        <v>405</v>
+        <v>355</v>
       </c>
       <c r="I204">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J204">
-        <v>6.0924</v>
+        <v>5.3403</v>
       </c>
       <c r="K204">
-        <v>2.3618</v>
+        <v>2.3768</v>
       </c>
       <c r="L204" t="s">
         <v>15</v>
@@ -9479,10 +9476,10 @@
         <v>205</v>
       </c>
       <c r="C206">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="D206">
-        <v>2164</v>
+        <v>2172</v>
       </c>
       <c r="E206">
         <v>92</v>
@@ -9494,16 +9491,16 @@
         <v>4</v>
       </c>
       <c r="H206">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="I206">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J206">
-        <v>6.3481</v>
+        <v>6.3933</v>
       </c>
       <c r="K206">
-        <v>3.3245</v>
+        <v>3.3546</v>
       </c>
       <c r="L206" t="s">
         <v>15</v>
@@ -9523,31 +9520,31 @@
         <v>206</v>
       </c>
       <c r="C207">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="D207">
-        <v>2165</v>
+        <v>2179</v>
       </c>
       <c r="E207">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F207">
-        <v>6082.12</v>
+        <v>6647.61</v>
       </c>
       <c r="G207">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H207">
-        <v>546</v>
+        <v>532</v>
       </c>
       <c r="I207">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="J207">
-        <v>8.9771</v>
+        <v>8.0029</v>
       </c>
       <c r="K207">
-        <v>2.4498</v>
+        <v>2.1963</v>
       </c>
       <c r="L207" t="s">
         <v>15</v>
@@ -9567,16 +9564,16 @@
         <v>207</v>
       </c>
       <c r="C208">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="D208">
-        <v>2166</v>
+        <v>2174</v>
       </c>
       <c r="E208">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F208">
-        <v>6361.73</v>
+        <v>5541.77</v>
       </c>
       <c r="G208">
         <v>0</v>
@@ -9658,28 +9655,28 @@
         <v>702</v>
       </c>
       <c r="D210">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="E210">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F210">
-        <v>6647.61</v>
+        <v>6361.73</v>
       </c>
       <c r="G210">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H210">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="I210">
-        <v>91</v>
+        <v>152</v>
       </c>
       <c r="J210">
-        <v>4.0165</v>
+        <v>4.4328</v>
       </c>
       <c r="K210">
-        <v>1.3689</v>
+        <v>2.3893</v>
       </c>
       <c r="L210" t="s">
         <v>15</v>
@@ -9699,10 +9696,10 @@
         <v>210</v>
       </c>
       <c r="C211">
-        <v>1914</v>
+        <v>1917</v>
       </c>
       <c r="D211">
-        <v>2169</v>
+        <v>2158</v>
       </c>
       <c r="E211">
         <v>92</v>
@@ -9714,13 +9711,13 @@
         <v>5</v>
       </c>
       <c r="H211">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="I211">
         <v>57</v>
       </c>
       <c r="J211">
-        <v>2.8281</v>
+        <v>2.9183</v>
       </c>
       <c r="K211">
         <v>0.8575</v>
@@ -9743,31 +9740,31 @@
         <v>211</v>
       </c>
       <c r="C212">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="D212">
-        <v>2170</v>
+        <v>2175</v>
       </c>
       <c r="E212">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F212">
-        <v>6361.73</v>
+        <v>6647.61</v>
       </c>
       <c r="G212">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H212">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="I212">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="J212">
-        <v>3.4267</v>
+        <v>3.5652</v>
       </c>
       <c r="K212">
-        <v>1.2732</v>
+        <v>1.1583</v>
       </c>
       <c r="L212" t="s">
         <v>15</v>
@@ -9787,10 +9784,10 @@
         <v>212</v>
       </c>
       <c r="C213">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="D213">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="E213">
         <v>88</v>
@@ -9799,16 +9796,16 @@
         <v>6082.12</v>
       </c>
       <c r="G213">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H213">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="I213">
         <v>59</v>
       </c>
       <c r="J213">
-        <v>4.6859</v>
+        <v>4.3406</v>
       </c>
       <c r="K213">
         <v>0.9701</v>
@@ -9878,28 +9875,28 @@
         <v>1605</v>
       </c>
       <c r="D215">
-        <v>2170</v>
+        <v>2169</v>
       </c>
       <c r="E215">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F215">
-        <v>6082.12</v>
+        <v>5808.8</v>
       </c>
       <c r="G215">
         <v>3</v>
       </c>
       <c r="H215">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="I215">
         <v>58</v>
       </c>
       <c r="J215">
-        <v>2.3676</v>
+        <v>2.4273</v>
       </c>
       <c r="K215">
-        <v>0.9536</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="L215" t="s">
         <v>15</v>
@@ -9963,31 +9960,31 @@
         <v>216</v>
       </c>
       <c r="C217">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="D217">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="E217">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F217">
-        <v>6082.12</v>
+        <v>5808.8</v>
       </c>
       <c r="G217">
         <v>4</v>
       </c>
       <c r="H217">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="I217">
         <v>45</v>
       </c>
       <c r="J217">
-        <v>2.2854</v>
+        <v>2.4273</v>
       </c>
       <c r="K217">
-        <v>0.7399</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="L217" t="s">
         <v>15</v>
@@ -10007,31 +10004,31 @@
         <v>217</v>
       </c>
       <c r="C218">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D218">
-        <v>2176</v>
+        <v>2172</v>
       </c>
       <c r="E218">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F218">
-        <v>6647.61</v>
+        <v>5808.8</v>
       </c>
       <c r="G218">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H218">
-        <v>257</v>
+        <v>216</v>
       </c>
       <c r="I218">
         <v>161</v>
       </c>
       <c r="J218">
-        <v>3.8661</v>
+        <v>3.7185</v>
       </c>
       <c r="K218">
-        <v>2.4219</v>
+        <v>2.7717</v>
       </c>
       <c r="L218" t="s">
         <v>15</v>
@@ -10054,7 +10051,7 @@
         <v>697</v>
       </c>
       <c r="D219">
-        <v>2278</v>
+        <v>2289</v>
       </c>
       <c r="E219">
         <v>92</v>
@@ -10063,16 +10060,16 @@
         <v>6647.61</v>
       </c>
       <c r="G219">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H219">
-        <v>263</v>
+        <v>177</v>
       </c>
       <c r="I219">
         <v>75</v>
       </c>
       <c r="J219">
-        <v>3.9563</v>
+        <v>2.6626</v>
       </c>
       <c r="K219">
         <v>1.1282</v>
@@ -10139,10 +10136,10 @@
         <v>220</v>
       </c>
       <c r="C221">
-        <v>1002</v>
+        <v>1008</v>
       </c>
       <c r="D221">
-        <v>2280</v>
+        <v>2292</v>
       </c>
       <c r="E221">
         <v>92</v>
@@ -10151,16 +10148,16 @@
         <v>6647.61</v>
       </c>
       <c r="G221">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H221">
-        <v>321</v>
+        <v>304</v>
       </c>
       <c r="I221">
         <v>165</v>
       </c>
       <c r="J221">
-        <v>4.8288</v>
+        <v>4.5731</v>
       </c>
       <c r="K221">
         <v>2.4821</v>
@@ -10183,10 +10180,10 @@
         <v>221</v>
       </c>
       <c r="C222">
-        <v>1153</v>
+        <v>1158</v>
       </c>
       <c r="D222">
-        <v>2282</v>
+        <v>2293</v>
       </c>
       <c r="E222">
         <v>92</v>
@@ -10195,19 +10192,19 @@
         <v>6647.61</v>
       </c>
       <c r="G222">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H222">
-        <v>252</v>
+        <v>199</v>
       </c>
       <c r="I222">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="J222">
-        <v>3.7908</v>
+        <v>2.9936</v>
       </c>
       <c r="K222">
-        <v>2.0158</v>
+        <v>1.3689</v>
       </c>
       <c r="L222" t="s">
         <v>15</v>
@@ -10315,10 +10312,10 @@
         <v>224</v>
       </c>
       <c r="C225">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="D225">
-        <v>2284</v>
+        <v>2290</v>
       </c>
       <c r="E225">
         <v>92</v>
@@ -10327,16 +10324,16 @@
         <v>6647.61</v>
       </c>
       <c r="G225">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H225">
-        <v>305</v>
+        <v>288</v>
       </c>
       <c r="I225">
         <v>87</v>
       </c>
       <c r="J225">
-        <v>4.5881</v>
+        <v>4.3324</v>
       </c>
       <c r="K225">
         <v>1.3087</v>
@@ -10359,10 +10356,10 @@
         <v>225</v>
       </c>
       <c r="C226">
-        <v>1305</v>
+        <v>1310</v>
       </c>
       <c r="D226">
-        <v>2287</v>
+        <v>2290</v>
       </c>
       <c r="E226">
         <v>92</v>
@@ -10371,16 +10368,16 @@
         <v>6647.61</v>
       </c>
       <c r="G226">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H226">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="I226">
         <v>73</v>
       </c>
       <c r="J226">
-        <v>1.7149</v>
+        <v>1.9706</v>
       </c>
       <c r="K226">
         <v>1.0981</v>
@@ -10491,31 +10488,31 @@
         <v>228</v>
       </c>
       <c r="C229">
-        <v>1610</v>
+        <v>1621</v>
       </c>
       <c r="D229">
-        <v>2288</v>
+        <v>2298</v>
       </c>
       <c r="E229">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F229">
-        <v>6361.73</v>
+        <v>6647.61</v>
       </c>
       <c r="G229">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H229">
-        <v>388</v>
+        <v>201</v>
       </c>
       <c r="I229">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="J229">
-        <v>6.099</v>
+        <v>3.0236</v>
       </c>
       <c r="K229">
-        <v>2.1378</v>
+        <v>1.8503</v>
       </c>
       <c r="L229" t="s">
         <v>15</v>
@@ -10535,10 +10532,10 @@
         <v>229</v>
       </c>
       <c r="C230">
-        <v>1762</v>
+        <v>1775</v>
       </c>
       <c r="D230">
-        <v>2291</v>
+        <v>2298</v>
       </c>
       <c r="E230">
         <v>92</v>
@@ -10547,19 +10544,19 @@
         <v>6647.61</v>
       </c>
       <c r="G230">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H230">
-        <v>300</v>
+        <v>109</v>
       </c>
       <c r="I230">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="J230">
-        <v>4.5129</v>
+        <v>1.6397</v>
       </c>
       <c r="K230">
-        <v>2.2865</v>
+        <v>1.038</v>
       </c>
       <c r="L230" t="s">
         <v>15</v>
@@ -10667,10 +10664,10 @@
         <v>232</v>
       </c>
       <c r="C233">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D233">
-        <v>2297</v>
+        <v>2287</v>
       </c>
       <c r="E233">
         <v>92</v>
@@ -10679,16 +10676,16 @@
         <v>6647.61</v>
       </c>
       <c r="G233">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H233">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="I233">
         <v>165</v>
       </c>
       <c r="J233">
-        <v>6.4986</v>
+        <v>6.9198</v>
       </c>
       <c r="K233">
         <v>2.4821</v>
@@ -10755,10 +10752,10 @@
         <v>234</v>
       </c>
       <c r="C235">
-        <v>844</v>
+        <v>850</v>
       </c>
       <c r="D235">
-        <v>2401</v>
+        <v>2412</v>
       </c>
       <c r="E235">
         <v>92</v>
@@ -10770,16 +10767,16 @@
         <v>2</v>
       </c>
       <c r="H235">
-        <v>182</v>
+        <v>92</v>
       </c>
       <c r="I235">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="J235">
-        <v>2.7378</v>
+        <v>1.384</v>
       </c>
       <c r="K235">
-        <v>1.5494</v>
+        <v>1.1433</v>
       </c>
       <c r="L235" t="s">
         <v>15</v>
@@ -10799,10 +10796,10 @@
         <v>235</v>
       </c>
       <c r="C236">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="D236">
-        <v>2401</v>
+        <v>2414</v>
       </c>
       <c r="E236">
         <v>92</v>
@@ -10811,19 +10808,19 @@
         <v>6647.61</v>
       </c>
       <c r="G236">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H236">
-        <v>210</v>
+        <v>321</v>
       </c>
       <c r="I236">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="J236">
-        <v>3.159</v>
+        <v>4.8288</v>
       </c>
       <c r="K236">
-        <v>1.0229</v>
+        <v>1.4441</v>
       </c>
       <c r="L236" t="s">
         <v>15</v>
@@ -10887,10 +10884,10 @@
         <v>237</v>
       </c>
       <c r="C238">
-        <v>1153</v>
+        <v>1160</v>
       </c>
       <c r="D238">
-        <v>2403</v>
+        <v>2413</v>
       </c>
       <c r="E238">
         <v>92</v>
@@ -10899,19 +10896,19 @@
         <v>6647.61</v>
       </c>
       <c r="G238">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H238">
-        <v>436</v>
+        <v>471</v>
       </c>
       <c r="I238">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="J238">
-        <v>6.5587</v>
+        <v>7.0853</v>
       </c>
       <c r="K238">
-        <v>1.4893</v>
+        <v>1.5494</v>
       </c>
       <c r="L238" t="s">
         <v>15</v>
@@ -10931,10 +10928,10 @@
         <v>238</v>
       </c>
       <c r="C239">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="D239">
-        <v>2404</v>
+        <v>2395</v>
       </c>
       <c r="E239">
         <v>92</v>
@@ -10946,16 +10943,16 @@
         <v>6</v>
       </c>
       <c r="H239">
-        <v>206</v>
+        <v>239</v>
       </c>
       <c r="I239">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J239">
-        <v>3.0989</v>
+        <v>3.5953</v>
       </c>
       <c r="K239">
-        <v>0.8875</v>
+        <v>0.9778</v>
       </c>
       <c r="L239" t="s">
         <v>15</v>
@@ -11019,10 +11016,10 @@
         <v>240</v>
       </c>
       <c r="C241">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="D241">
-        <v>2410</v>
+        <v>2415</v>
       </c>
       <c r="E241">
         <v>92</v>
@@ -11034,16 +11031,16 @@
         <v>5</v>
       </c>
       <c r="H241">
-        <v>617</v>
+        <v>471</v>
       </c>
       <c r="I241">
-        <v>227</v>
+        <v>174</v>
       </c>
       <c r="J241">
-        <v>9.281499999999999</v>
+        <v>7.0853</v>
       </c>
       <c r="K241">
-        <v>3.4148</v>
+        <v>2.6175</v>
       </c>
       <c r="L241" t="s">
         <v>15</v>
@@ -11107,10 +11104,10 @@
         <v>242</v>
       </c>
       <c r="C243">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="D243">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="E243">
         <v>90</v>
@@ -11122,16 +11119,16 @@
         <v>4</v>
       </c>
       <c r="H243">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="I243">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="J243">
-        <v>3.3481</v>
+        <v>3.018</v>
       </c>
       <c r="K243">
-        <v>1.2418</v>
+        <v>1.0689</v>
       </c>
       <c r="L243" t="s">
         <v>15</v>
@@ -11154,28 +11151,28 @@
         <v>1922</v>
       </c>
       <c r="D244">
-        <v>2410</v>
+        <v>2409</v>
       </c>
       <c r="E244">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F244">
-        <v>6361.73</v>
+        <v>6082.12</v>
       </c>
       <c r="G244">
         <v>4</v>
       </c>
       <c r="H244">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="I244">
         <v>150</v>
       </c>
       <c r="J244">
-        <v>5.8475</v>
+        <v>5.9848</v>
       </c>
       <c r="K244">
-        <v>2.3579</v>
+        <v>2.4662</v>
       </c>
       <c r="L244" t="s">
         <v>15</v>
@@ -11239,10 +11236,10 @@
         <v>245</v>
       </c>
       <c r="C246">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="D246">
-        <v>2417</v>
+        <v>2410</v>
       </c>
       <c r="E246">
         <v>92</v>
@@ -11254,13 +11251,13 @@
         <v>7</v>
       </c>
       <c r="H246">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="I246">
         <v>72</v>
       </c>
       <c r="J246">
-        <v>5.7314</v>
+        <v>5.6562</v>
       </c>
       <c r="K246">
         <v>1.0831</v>
@@ -11283,10 +11280,10 @@
         <v>246</v>
       </c>
       <c r="C247">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D247">
-        <v>2418</v>
+        <v>2409</v>
       </c>
       <c r="E247">
         <v>92</v>
@@ -11298,16 +11295,16 @@
         <v>3</v>
       </c>
       <c r="H247">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="I247">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="J247">
-        <v>2.9334</v>
+        <v>2.9635</v>
       </c>
       <c r="K247">
-        <v>1.5043</v>
+        <v>1.6547</v>
       </c>
       <c r="L247" t="s">
         <v>15</v>
@@ -11327,37 +11324,37 @@
         <v>247</v>
       </c>
       <c r="C248">
-        <v>2103</v>
+        <v>2149</v>
       </c>
       <c r="D248">
-        <v>1616</v>
+        <v>1604</v>
       </c>
       <c r="E248">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="F248">
-        <v>4071.5</v>
+        <v>5281.02</v>
       </c>
       <c r="G248">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H248">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="I248">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="J248">
-        <v>0</v>
+        <v>5.4535</v>
       </c>
       <c r="K248">
-        <v>0</v>
+        <v>4.431</v>
       </c>
       <c r="L248" t="s">
         <v>15</v>
       </c>
       <c r="M248" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N248">
         <v>0.2</v>
@@ -11371,10 +11368,10 @@
         <v>248</v>
       </c>
       <c r="C249">
-        <v>2103</v>
+        <v>2155</v>
       </c>
       <c r="D249">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="E249">
         <v>72</v>
@@ -11386,22 +11383,22 @@
         <v>1</v>
       </c>
       <c r="H249">
-        <v>731</v>
+        <v>145</v>
       </c>
       <c r="I249">
-        <v>731</v>
+        <v>145</v>
       </c>
       <c r="J249">
-        <v>17.9541</v>
+        <v>3.5613</v>
       </c>
       <c r="K249">
-        <v>17.9541</v>
+        <v>3.5613</v>
       </c>
       <c r="L249" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M249" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N249">
         <v>0.2</v>
@@ -11415,37 +11412,37 @@
         <v>249</v>
       </c>
       <c r="C250">
-        <v>344</v>
+        <v>294</v>
       </c>
       <c r="D250">
         <v>1829</v>
       </c>
       <c r="E250">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F250">
-        <v>4071.5</v>
+        <v>3848.45</v>
       </c>
       <c r="G250">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H250">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="I250">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="J250">
-        <v>0</v>
+        <v>3.2481</v>
       </c>
       <c r="K250">
-        <v>0</v>
+        <v>0.8055</v>
       </c>
       <c r="L250" t="s">
         <v>15</v>
       </c>
       <c r="M250" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N250">
         <v>0.2</v>
@@ -11459,37 +11456,37 @@
         <v>250</v>
       </c>
       <c r="C251">
-        <v>344</v>
+        <v>285</v>
       </c>
       <c r="D251">
         <v>2054</v>
       </c>
       <c r="E251">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F251">
-        <v>4300.84</v>
+        <v>3631.68</v>
       </c>
       <c r="G251">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H251">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="I251">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J251">
-        <v>1.2091</v>
+        <v>2.368</v>
       </c>
       <c r="K251">
-        <v>1.2091</v>
+        <v>1.3768</v>
       </c>
       <c r="L251" t="s">
         <v>15</v>
       </c>
       <c r="M251" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N251">
         <v>0.2</v>
@@ -11503,37 +11500,37 @@
         <v>251</v>
       </c>
       <c r="C252">
-        <v>2103</v>
+        <v>2169</v>
       </c>
       <c r="D252">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="E252">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F252">
-        <v>4071.5</v>
+        <v>3631.68</v>
       </c>
       <c r="G252">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H252">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="I252">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="J252">
-        <v>0</v>
+        <v>4.626</v>
       </c>
       <c r="K252">
-        <v>0</v>
+        <v>4.626</v>
       </c>
       <c r="L252" t="s">
         <v>15</v>
       </c>
       <c r="M252" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N252">
         <v>0.2</v>
@@ -11547,16 +11544,16 @@
         <v>252</v>
       </c>
       <c r="C253">
-        <v>458</v>
+        <v>410</v>
       </c>
       <c r="D253">
-        <v>2170</v>
+        <v>2174</v>
       </c>
       <c r="E253">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F253">
-        <v>5281.02</v>
+        <v>4300.84</v>
       </c>
       <c r="G253">
         <v>0</v>
@@ -11577,7 +11574,7 @@
         <v>15</v>
       </c>
       <c r="M253" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N253">
         <v>0.2</v>
@@ -11635,37 +11632,37 @@
         <v>254</v>
       </c>
       <c r="C255">
-        <v>1974</v>
+        <v>2037</v>
       </c>
       <c r="D255">
-        <v>2287</v>
+        <v>2291</v>
       </c>
       <c r="E255">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F255">
-        <v>4071.5</v>
+        <v>3631.68</v>
       </c>
       <c r="G255">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H255">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="I255">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="J255">
-        <v>0</v>
+        <v>3.6898</v>
       </c>
       <c r="K255">
-        <v>0</v>
+        <v>3.084</v>
       </c>
       <c r="L255" t="s">
         <v>15</v>
       </c>
       <c r="M255" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N255">
         <v>0.2</v>
@@ -11679,37 +11676,37 @@
         <v>255</v>
       </c>
       <c r="C256">
-        <v>458</v>
+        <v>514</v>
       </c>
       <c r="D256">
-        <v>2408</v>
+        <v>2411</v>
       </c>
       <c r="E256">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="F256">
-        <v>4536.46</v>
+        <v>3631.68</v>
       </c>
       <c r="G256">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H256">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="I256">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="J256">
-        <v>0</v>
+        <v>4.0202</v>
       </c>
       <c r="K256">
-        <v>0</v>
+        <v>3.4144</v>
       </c>
       <c r="L256" t="s">
         <v>15</v>
       </c>
       <c r="M256" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N256">
         <v>0.2</v>
@@ -11723,37 +11720,37 @@
         <v>256</v>
       </c>
       <c r="C257">
-        <v>1860</v>
+        <v>1797</v>
       </c>
       <c r="D257">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="E257">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F257">
-        <v>4071.5</v>
+        <v>3631.68</v>
       </c>
       <c r="G257">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H257">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="I257">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="J257">
-        <v>0</v>
+        <v>1.0739</v>
       </c>
       <c r="K257">
-        <v>0</v>
+        <v>0.5782</v>
       </c>
       <c r="L257" t="s">
         <v>15</v>
       </c>
       <c r="M257" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N257">
         <v>0.2</v>
@@ -11788,40 +11785,40 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>19</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>20</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>22</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>23</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>24</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>25</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>26</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>27</v>
-      </c>
-      <c r="M1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -11832,19 +11829,19 @@
         <v>256</v>
       </c>
       <c r="C2">
-        <v>3.2931</v>
+        <v>3.4669</v>
       </c>
       <c r="D2">
-        <v>17.9541</v>
+        <v>13.8799</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2">
         <v>25</v>
@@ -11853,16 +11850,16 @@
         <v>12</v>
       </c>
       <c r="J2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
